--- a/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,55 +362,60 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>area_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>tot_cases</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>tot_cases_low</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tot_cases_up</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>tot_daly</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tot_daly_low</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tot_daly_up</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tot_medic_costs</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tot_medic_costs_low</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tot_soc_costs_up</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tot_soc_costs</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tot_soc_costs_low</t>
         </is>
@@ -422,37 +427,42 @@
           <t>mort</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
+      </c>
+      <c r="C2">
         <v>16752.394</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>16094.655</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>17411.444</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>152575.08</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>149843.095</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>155261.519</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>20648620987.93</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>20290908039.326</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>19933286637.138</v>
       </c>
     </row>
@@ -462,37 +472,42 @@
           <t>mort</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="C3">
         <v>16471.484</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>15924.705</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>17010.27</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>141667.547</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>140890.514</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>142404.655</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>18942522208.029</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>18842343021.661</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>18739593300.739</v>
       </c>
     </row>
@@ -502,37 +517,42 @@
           <t>mort</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="C4">
         <v>8082.210999999999</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>7930.574000000001</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>8234.926999999996</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>76180.55599999998</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>76539.69500000001</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>75834.40800000005</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>10087968389.916</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>10134821564.21301</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>10173111763.133</v>
       </c>
     </row>
@@ -542,37 +562,42 @@
           <t>cvd</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
+      </c>
+      <c r="C5">
         <v>8049.442999999999</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>7993.989999999998</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>8104.995000000001</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>6213.906000000001</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>6214.254000000001</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>6209.797999999999</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>448425726.816</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>445417755.6079999</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>825659016.8069999</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>826427314.102</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>826939734.302</v>
       </c>
     </row>
@@ -582,37 +607,42 @@
           <t>cvd</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="C6">
         <v>5916.046</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>6036.901</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>5789.533000000001</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>4135.518</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>4324.834</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>3933.937999999998</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>329500228.6719999</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>336364918.1249999</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>523125732.2939999</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>549817295.8970001</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>574872854.952</v>
       </c>
     </row>
@@ -622,37 +652,42 @@
           <t>cvd</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="C7">
         <v>592.6359999999986</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>864.2920000000013</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>322.3229999999967</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-245.6819999999971</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>29.46299999999974</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-526.018</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>32913251.7809999</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>48011316.329</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>-69225665.73500013</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>-32739716.58700037</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>4078201.59499979</v>
       </c>
     </row>
@@ -662,37 +697,42 @@
           <t>cancer</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
+      </c>
+      <c r="C8">
         <v>2422.797</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>2717.489</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>2103.942000000001</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>2409.219000000001</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>3023.745999999999</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1664.476999999999</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>35874282.97600001</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>40235062.609</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>221193256.4419999</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>320471773.766</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>402595073.017</v>
       </c>
     </row>
@@ -702,37 +742,42 @@
           <t>cancer</t>
         </is>
       </c>
-      <c r="B9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="C9">
         <v>1043.576999999999</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>1368.508</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>687.9649999999992</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>589.5869999999995</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>1163.380999999999</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>-63.58899999999994</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>15483867.37300001</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>20305123.558</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>-8339660.927999973</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>78844980.75199986</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>154000547.2510002</v>
       </c>
     </row>
@@ -742,37 +787,42 @@
           <t>cancer</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="C10">
         <v>-4065.107</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-3484.107000000002</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-4684.091</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-7611.713</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>-6455.915000000001</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>-8861.604000000003</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>-60208020.68200001</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>-51552497.48800001</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>-1178387870.658</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>-1012141267.773</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>-859152484.2059999</v>
       </c>
     </row>
@@ -782,37 +832,42 @@
           <t>diab2</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
+      </c>
+      <c r="C11">
         <v>461.268</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>510.0710000000001</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>408.7640000000001</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>776.0330000000004</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>869.1779999999999</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>677.5719999999997</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>34686899.78199999</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>38370985.06200001</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>90063074.24300003</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>103212085.663</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>115477503.658</v>
       </c>
     </row>
@@ -822,37 +877,42 @@
           <t>diab2</t>
         </is>
       </c>
-      <c r="B12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="C12">
         <v>148.8040000000001</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>216.694</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>75.67900000000009</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>169.5640000000003</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>304.0070000000001</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>23.38900000000012</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>11181823.73100001</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>16246172.48900001</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>3264982.771999955</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>22612508.60100001</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>40283823.00199997</v>
       </c>
     </row>
@@ -862,37 +922,42 @@
           <t>diab2</t>
         </is>
       </c>
-      <c r="B13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="C13">
         <v>-859.0769999999998</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>-746.7690000000002</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>-975.54</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>-1911.745</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>-1666.121</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>-2173.35</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>-64624372.449</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>-56130368.71900001</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>-288848928.3660001</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>-254195513.51</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>-221313725.09</v>
       </c>
     </row>
@@ -902,37 +967,42 @@
           <t>dem</t>
         </is>
       </c>
-      <c r="B14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
+      </c>
+      <c r="C14">
         <v>3044.339</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>2989.208</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>3096.800999999999</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>4389.900000000001</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>4385.867999999999</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>4387.712999999999</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>51265644.68100001</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>50319417.594</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>583389884.0999999</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>583722285.136</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>583639390.0679998</v>
       </c>
     </row>
@@ -942,37 +1012,42 @@
           <t>dem</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="C15">
         <v>2347.096</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>2360.909</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>2326.692</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>2780.335999999999</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>2886.152</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>2667.485000000001</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>39521469.156</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>39758715.156</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>354487539.5259999</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>369736806.2399999</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>383749383.898</v>
       </c>
     </row>
@@ -982,37 +1057,42 @@
           <t>dem</t>
         </is>
       </c>
-      <c r="B16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="C16">
         <v>363.1639999999998</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>484.4159999999993</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>241.8400000000001</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-77.65599999999904</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>130.4279999999999</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>-287.7090000000007</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>6127148.941999987</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>8120784.795000002</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>-38321154.09599996</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>-10508388.76999998</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>17077931.1329999</v>
       </c>
     </row>
@@ -1022,37 +1102,42 @@
           <t>dep</t>
         </is>
       </c>
-      <c r="B17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
+      </c>
+      <c r="C17">
         <v>9901.088</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>10885.866</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>8844.025000000001</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>2273.705</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>2765.363</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>1679.292000000001</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <v>222981343.7490001</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>302353958.5869999</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>368030554.135</v>
       </c>
     </row>
@@ -1062,37 +1147,42 @@
           <t>dep</t>
         </is>
       </c>
-      <c r="B18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="C18">
         <v>4096.823</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>5076.526999999998</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>3106.748000000003</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>650.9430000000011</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>1035.459</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>246.8220000000001</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
         <v>32453154.32400012</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>86452883.36800015</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>137799441.723</v>
       </c>
     </row>
@@ -1102,37 +1192,42 @@
           <t>dep</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="C19">
         <v>-15576.306</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>-13656.873</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>-17525.03000000001</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>-6024.174999999999</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>-5175.860000000001</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>-6904.485000000001</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
         <v>-919296434.0240002</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>-801578852.099</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>-688313943.072</v>
       </c>
     </row>
@@ -1142,37 +1237,42 @@
           <t>cancer</t>
         </is>
       </c>
-      <c r="B20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C20">
         <v>-598.7330000000002</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>601.8899999999994</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>-1892.183999999987</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>-4612.906999999999</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>-2268.788</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>-7260.716</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>-8849870.332999945</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>8987688.67900002</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>-965534275.1439991</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>-612824513.2550001</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>-302556863.9379997</v>
       </c>
     </row>
@@ -1182,37 +1282,42 @@
           <t>cvd</t>
         </is>
       </c>
-      <c r="B21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C21">
         <v>14558.12499999999</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>14895.18300000001</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>14216.851</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>10103.74200000001</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>10568.551</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>9617.718000000001</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>810839207.2690001</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>829793990.0619998</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>1279559083.365999</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>1343504893.412001</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>1405890790.848999</v>
       </c>
     </row>
@@ -1222,37 +1327,42 @@
           <t>dem</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C22">
         <v>5754.599</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>5834.532999999999</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>5665.332999999999</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>7092.580000000002</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>7402.448</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>6767.488999999998</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>96914262.77900001</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>98198917.54500002</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>899556269.5299997</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>942950702.6059999</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>984466705.099</v>
       </c>
     </row>
@@ -1262,37 +1372,42 @@
           <t>dep</t>
         </is>
       </c>
-      <c r="B23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C23">
         <v>-1578.39499999999</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>2305.51999999999</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-5574.256999999983</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-3099.527000000002</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>-1375.038</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>-4978.370999999999</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>-663861935.9509993</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>-412772010.1439991</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>-182483947.2139997</v>
       </c>
     </row>
@@ -1302,37 +1417,42 @@
           <t>diab2</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C24">
         <v>-249.005000000001</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>-20.00400000000081</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>-491.0969999999988</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>-966.1479999999992</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>-492.9359999999997</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>-1472.388999999999</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>-18755648.93600005</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>-1513211.167999983</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>-195520871.3510001</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>-128370919.2460001</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>-65552398.43000007</v>
       </c>
     </row>
@@ -1342,37 +1462,42 @@
           <t>mort</t>
         </is>
       </c>
-      <c r="B25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C25">
         <v>41306.08899999999</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>39949.934</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>42656.641</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>370423.1830000002</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>367273.3040000001</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>373500.5820000001</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>49679111585.875</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>49268072625.20001</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>48845991701.00999</v>
       </c>
     </row>
@@ -1382,37 +1507,42 @@
           <t>All</t>
         </is>
       </c>
-      <c r="B26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
+      </c>
+      <c r="C26">
         <v>40631.32900000001</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>41191.27900000001</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>39969.97099999999</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>168637.843</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>167101.504</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>169880.371</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>570252554.255</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>574343220.873</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>22591907563.27101</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>22427095456.58001</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>22229968892.318</v>
       </c>
     </row>
@@ -1422,37 +1552,42 @@
           <t>All</t>
         </is>
       </c>
-      <c r="B27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="C27">
         <v>30023.82999999999</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>30984.24400000001</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>28996.887</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>149993.495</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>150604.347</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>149212.7000000001</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>395687388.932</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>412674929.3280001</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>19847513956.017</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>19949807496.519</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>20030299351.56499</v>
       </c>
     </row>
@@ -1462,37 +1597,42 @@
           <t>All</t>
         </is>
       </c>
-      <c r="B28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="C28">
         <v>-11462.47900000001</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>-8608.467000000004</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>-14385.571</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>60309.5849999999</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>63401.68999999994</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>57081.24200000014</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>-85791992.40799999</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>-51550765.08299994</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>7593888337.03701</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>8023657825.473999</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>8425487743.492996</v>
       </c>
     </row>
@@ -1502,37 +1642,42 @@
           <t>All</t>
         </is>
       </c>
-      <c r="B29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C29">
         <v>59192.67999999999</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>63567.05599999998</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>54581.28699999989</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>378940.9230000001</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>381107.5409999999</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>376174.313</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>880147950.7789998</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>935467385.118</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>50033309856.3251</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>50400560778.573</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>50685755987.37599</v>
       </c>
     </row>
@@ -1542,37 +1687,42 @@
           <t>Morbidity</t>
         </is>
       </c>
-      <c r="B30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C30">
         <v>17886.59100000001</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>23617.122</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>11924.64599999998</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>8517.739999999991</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>13834.23700000002</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>2673.730999999883</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>880147950.7789998</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>935467385.118</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>354198270.4500008</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>1132488153.372997</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>1839764286.365997</v>
       </c>
     </row>

--- a/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -407,17 +407,22 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
         </is>
       </c>
     </row>
@@ -457,7 +462,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>20648620987.93</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>20290908039.326</v>
@@ -465,6 +470,9 @@
       <c r="M2">
         <v>19933286637.138</v>
       </c>
+      <c r="N2">
+        <v>20648620987.93</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -502,7 +510,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>18942522208.029</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>18842343021.661</v>
@@ -510,6 +518,9 @@
       <c r="M3">
         <v>18739593300.739</v>
       </c>
+      <c r="N3">
+        <v>18942522208.029</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -547,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>10087968389.916</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>10134821564.21301</v>
@@ -555,6 +566,9 @@
       <c r="M4">
         <v>10173111763.133</v>
       </c>
+      <c r="N4">
+        <v>10087968389.916</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -592,7 +606,7 @@
         <v>445417755.6079999</v>
       </c>
       <c r="K5">
-        <v>825659016.8069999</v>
+        <v>451244564.948</v>
       </c>
       <c r="L5">
         <v>826427314.102</v>
@@ -600,6 +614,9 @@
       <c r="M5">
         <v>826939734.302</v>
       </c>
+      <c r="N5">
+        <v>825659016.8069999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -637,7 +654,7 @@
         <v>336364918.1249999</v>
       </c>
       <c r="K6">
-        <v>523125732.2939999</v>
+        <v>322333314.5879999</v>
       </c>
       <c r="L6">
         <v>549817295.8970001</v>
@@ -645,6 +662,9 @@
       <c r="M6">
         <v>574872854.952</v>
       </c>
+      <c r="N6">
+        <v>523125732.2939999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -682,7 +702,7 @@
         <v>48011316.329</v>
       </c>
       <c r="K7">
-        <v>-69225665.73500013</v>
+        <v>17989835.58799982</v>
       </c>
       <c r="L7">
         <v>-32739716.58700037</v>
@@ -690,6 +710,9 @@
       <c r="M7">
         <v>4078201.59499979</v>
       </c>
+      <c r="N7">
+        <v>-69225665.73500013</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -727,7 +750,7 @@
         <v>40235062.609</v>
       </c>
       <c r="K8">
-        <v>221193256.4419999</v>
+        <v>31092607.04700001</v>
       </c>
       <c r="L8">
         <v>320471773.766</v>
@@ -735,6 +758,9 @@
       <c r="M8">
         <v>402595073.017</v>
       </c>
+      <c r="N8">
+        <v>221193256.4419999</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,7 +798,7 @@
         <v>20305123.558</v>
       </c>
       <c r="K9">
-        <v>-8339660.927999973</v>
+        <v>10175059.06</v>
       </c>
       <c r="L9">
         <v>78844980.75199986</v>
@@ -780,6 +806,9 @@
       <c r="M9">
         <v>154000547.2510002</v>
       </c>
+      <c r="N9">
+        <v>-8339660.927999973</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -817,7 +846,7 @@
         <v>-51552497.48800001</v>
       </c>
       <c r="K10">
-        <v>-1178387870.658</v>
+        <v>-69432129.67099997</v>
       </c>
       <c r="L10">
         <v>-1012141267.773</v>
@@ -825,6 +854,9 @@
       <c r="M10">
         <v>-859152484.2059999</v>
       </c>
+      <c r="N10">
+        <v>-1178387870.658</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -862,7 +894,7 @@
         <v>38370985.06200001</v>
       </c>
       <c r="K11">
-        <v>90063074.24300003</v>
+        <v>30702017.792</v>
       </c>
       <c r="L11">
         <v>103212085.663</v>
@@ -870,6 +902,9 @@
       <c r="M11">
         <v>115477503.658</v>
       </c>
+      <c r="N11">
+        <v>90063074.24300003</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -907,7 +942,7 @@
         <v>16246172.48900001</v>
       </c>
       <c r="K12">
-        <v>3264982.771999955</v>
+        <v>5703051.00500001</v>
       </c>
       <c r="L12">
         <v>22612508.60100001</v>
@@ -915,6 +950,9 @@
       <c r="M12">
         <v>40283823.00199997</v>
       </c>
+      <c r="N12">
+        <v>3264982.771999955</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -952,7 +990,7 @@
         <v>-56130368.71900001</v>
       </c>
       <c r="K13">
-        <v>-288848928.3660001</v>
+        <v>-73392910.942</v>
       </c>
       <c r="L13">
         <v>-254195513.51</v>
@@ -960,6 +998,9 @@
       <c r="M13">
         <v>-221313725.09</v>
       </c>
+      <c r="N13">
+        <v>-288848928.3660001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -997,7 +1038,7 @@
         <v>50319417.594</v>
       </c>
       <c r="K14">
-        <v>583389884.0999999</v>
+        <v>52150438.421</v>
       </c>
       <c r="L14">
         <v>583722285.136</v>
@@ -1005,6 +1046,9 @@
       <c r="M14">
         <v>583639390.0679998</v>
       </c>
+      <c r="N14">
+        <v>583389884.0999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1042,7 +1086,7 @@
         <v>39758715.156</v>
       </c>
       <c r="K15">
-        <v>354487539.5259999</v>
+        <v>39198700.91599999</v>
       </c>
       <c r="L15">
         <v>369736806.2399999</v>
@@ -1050,6 +1094,9 @@
       <c r="M15">
         <v>383749383.898</v>
       </c>
+      <c r="N15">
+        <v>354487539.5259999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1087,7 +1134,7 @@
         <v>8120784.795000002</v>
       </c>
       <c r="K16">
-        <v>-38321154.09599996</v>
+        <v>4052198.366999999</v>
       </c>
       <c r="L16">
         <v>-10508388.76999998</v>
@@ -1095,6 +1142,9 @@
       <c r="M16">
         <v>17077931.1329999</v>
       </c>
+      <c r="N16">
+        <v>-38321154.09599996</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1132,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>222981343.7490001</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>302353958.5869999</v>
@@ -1140,6 +1190,9 @@
       <c r="M17">
         <v>368030554.135</v>
       </c>
+      <c r="N17">
+        <v>222981343.7490001</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1177,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>32453154.32400012</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>86452883.36800015</v>
@@ -1185,6 +1238,9 @@
       <c r="M18">
         <v>137799441.723</v>
       </c>
+      <c r="N18">
+        <v>32453154.32400012</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1222,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>-919296434.0240002</v>
+        <v>0</v>
       </c>
       <c r="L19">
         <v>-801578852.099</v>
@@ -1230,6 +1286,9 @@
       <c r="M19">
         <v>-688313943.072</v>
       </c>
+      <c r="N19">
+        <v>-919296434.0240002</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1267,7 +1326,7 @@
         <v>8987688.67900002</v>
       </c>
       <c r="K20">
-        <v>-965534275.1439991</v>
+        <v>-28164463.56399995</v>
       </c>
       <c r="L20">
         <v>-612824513.2550001</v>
@@ -1275,6 +1334,9 @@
       <c r="M20">
         <v>-302556863.9379997</v>
       </c>
+      <c r="N20">
+        <v>-965534275.1439991</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1312,7 +1374,7 @@
         <v>829793990.0619998</v>
       </c>
       <c r="K21">
-        <v>1279559083.365999</v>
+        <v>791567715.1239996</v>
       </c>
       <c r="L21">
         <v>1343504893.412001</v>
@@ -1320,6 +1382,9 @@
       <c r="M21">
         <v>1405890790.848999</v>
       </c>
+      <c r="N21">
+        <v>1279559083.365999</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1357,7 +1422,7 @@
         <v>98198917.54500002</v>
       </c>
       <c r="K22">
-        <v>899556269.5299997</v>
+        <v>95401337.70400003</v>
       </c>
       <c r="L22">
         <v>942950702.6059999</v>
@@ -1365,6 +1430,9 @@
       <c r="M22">
         <v>984466705.099</v>
       </c>
+      <c r="N22">
+        <v>899556269.5299997</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1402,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>-663861935.9509993</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <v>-412772010.1439991</v>
@@ -1410,6 +1478,9 @@
       <c r="M23">
         <v>-182483947.2139997</v>
       </c>
+      <c r="N23">
+        <v>-663861935.9509993</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1447,7 +1518,7 @@
         <v>-1513211.167999983</v>
       </c>
       <c r="K24">
-        <v>-195520871.3510001</v>
+        <v>-36987842.14500004</v>
       </c>
       <c r="L24">
         <v>-128370919.2460001</v>
@@ -1455,6 +1526,9 @@
       <c r="M24">
         <v>-65552398.43000007</v>
       </c>
+      <c r="N24">
+        <v>-195520871.3510001</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1492,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>49679111585.875</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>49268072625.20001</v>
@@ -1500,6 +1574,9 @@
       <c r="M25">
         <v>48845991701.00999</v>
       </c>
+      <c r="N25">
+        <v>49679111585.875</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1537,7 +1614,7 @@
         <v>574343220.873</v>
       </c>
       <c r="K26">
-        <v>22591907563.27101</v>
+        <v>565189628.2079999</v>
       </c>
       <c r="L26">
         <v>22427095456.58001</v>
@@ -1545,6 +1622,9 @@
       <c r="M26">
         <v>22229968892.318</v>
       </c>
+      <c r="N26">
+        <v>22591907563.27101</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1582,7 +1662,7 @@
         <v>412674929.3280001</v>
       </c>
       <c r="K27">
-        <v>19847513956.017</v>
+        <v>377410125.5690001</v>
       </c>
       <c r="L27">
         <v>19949807496.519</v>
@@ -1590,6 +1670,9 @@
       <c r="M27">
         <v>20030299351.56499</v>
       </c>
+      <c r="N27">
+        <v>19847513956.017</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1627,7 +1710,7 @@
         <v>-51550765.08299994</v>
       </c>
       <c r="K28">
-        <v>7593888337.03701</v>
+        <v>-120783006.658</v>
       </c>
       <c r="L28">
         <v>8023657825.473999</v>
@@ -1635,6 +1718,9 @@
       <c r="M28">
         <v>8425487743.492996</v>
       </c>
+      <c r="N28">
+        <v>7593888337.03701</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1672,7 +1758,7 @@
         <v>935467385.118</v>
       </c>
       <c r="K29">
-        <v>50033309856.3251</v>
+        <v>821816747.1190004</v>
       </c>
       <c r="L29">
         <v>50400560778.573</v>
@@ -1680,6 +1766,9 @@
       <c r="M29">
         <v>50685755987.37599</v>
       </c>
+      <c r="N29">
+        <v>50033309856.3251</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1717,13 +1806,16 @@
         <v>935467385.118</v>
       </c>
       <c r="K30">
-        <v>354198270.4500008</v>
+        <v>821816747.1190004</v>
       </c>
       <c r="L30">
         <v>1132488153.372997</v>
       </c>
       <c r="M30">
         <v>1839764286.365997</v>
+      </c>
+      <c r="N30">
+        <v>354198270.4500008</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
@@ -1,21 +1,123 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C40D54-6B55-EF4F-9E29-BD9F9FC360DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="24680" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$30</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>area_type</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>periurban</t>
+  </si>
+  <si>
+    <t>rural</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +165,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +217,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +251,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +286,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,104 +462,83 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>area_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
         <v>16752.394</v>
       </c>
       <c r="D2">
-        <v>16094.655</v>
+        <v>16094.655000000001</v>
       </c>
       <c r="E2">
         <v>17411.444</v>
       </c>
       <c r="F2">
-        <v>152575.08</v>
+        <v>152575.07999999999</v>
       </c>
       <c r="G2">
         <v>149843.095</v>
@@ -474,16 +565,12 @@
         <v>20648620987.93</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
         <v>16471.484</v>
@@ -495,7 +582,7 @@
         <v>17010.27</v>
       </c>
       <c r="F3">
-        <v>141667.547</v>
+        <v>141667.54699999999</v>
       </c>
       <c r="G3">
         <v>140890.514</v>
@@ -513,43 +600,39 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>18842343021.661</v>
+        <v>18842343021.660999</v>
       </c>
       <c r="M3">
-        <v>18739593300.739</v>
+        <v>18739593300.738998</v>
       </c>
       <c r="N3">
-        <v>18942522208.029</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>18942522208.028999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
-        <v>8082.210999999999</v>
+        <v>8082.2109999999993</v>
       </c>
       <c r="D4">
-        <v>7930.574000000001</v>
+        <v>7930.5740000000014</v>
       </c>
       <c r="E4">
         <v>8234.926999999996</v>
       </c>
       <c r="F4">
-        <v>76180.55599999998</v>
+        <v>76180.555999999982</v>
       </c>
       <c r="G4">
-        <v>76539.69500000001</v>
+        <v>76539.695000000007</v>
       </c>
       <c r="H4">
-        <v>75834.40800000005</v>
+        <v>75834.408000000054</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,169 +644,153 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>10134821564.21301</v>
+        <v>10134821564.213011</v>
       </c>
       <c r="M4">
-        <v>10173111763.133</v>
+        <v>10173111763.132999</v>
       </c>
       <c r="N4">
         <v>10087968389.916</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>8049.442999999999</v>
+        <v>8049.4429999999993</v>
       </c>
       <c r="D5">
         <v>7993.989999999998</v>
       </c>
       <c r="E5">
-        <v>8104.995000000001</v>
+        <v>8104.9950000000008</v>
       </c>
       <c r="F5">
-        <v>6213.906000000001</v>
+        <v>6213.9060000000009</v>
       </c>
       <c r="G5">
-        <v>6214.254000000001</v>
+        <v>6214.2540000000008</v>
       </c>
       <c r="H5">
-        <v>6209.797999999999</v>
+        <v>6209.7979999999989</v>
       </c>
       <c r="I5">
-        <v>448425726.816</v>
+        <v>448425726.81599998</v>
       </c>
       <c r="J5">
-        <v>445417755.6079999</v>
+        <v>445417755.60799992</v>
       </c>
       <c r="K5">
-        <v>451244564.948</v>
+        <v>451244564.94800001</v>
       </c>
       <c r="L5">
         <v>826427314.102</v>
       </c>
       <c r="M5">
-        <v>826939734.302</v>
+        <v>826939734.30200005</v>
       </c>
       <c r="N5">
-        <v>825659016.8069999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>825659016.80699992</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>5916.046</v>
+        <v>5916.0460000000003</v>
       </c>
       <c r="D6">
-        <v>6036.901</v>
+        <v>6036.9009999999998</v>
       </c>
       <c r="E6">
-        <v>5789.533000000001</v>
+        <v>5789.5330000000013</v>
       </c>
       <c r="F6">
         <v>4135.518</v>
       </c>
       <c r="G6">
-        <v>4324.834</v>
+        <v>4324.8339999999998</v>
       </c>
       <c r="H6">
-        <v>3933.937999999998</v>
+        <v>3933.9379999999978</v>
       </c>
       <c r="I6">
-        <v>329500228.6719999</v>
+        <v>329500228.67199987</v>
       </c>
       <c r="J6">
-        <v>336364918.1249999</v>
+        <v>336364918.12499988</v>
       </c>
       <c r="K6">
-        <v>322333314.5879999</v>
+        <v>322333314.58799988</v>
       </c>
       <c r="L6">
-        <v>549817295.8970001</v>
+        <v>549817295.89700007</v>
       </c>
       <c r="M6">
-        <v>574872854.952</v>
+        <v>574872854.95200002</v>
       </c>
       <c r="N6">
-        <v>523125732.2939999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>523125732.29399991</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
       </c>
       <c r="C7">
         <v>592.6359999999986</v>
       </c>
       <c r="D7">
-        <v>864.2920000000013</v>
+        <v>864.29200000000128</v>
       </c>
       <c r="E7">
-        <v>322.3229999999967</v>
+        <v>322.32299999999668</v>
       </c>
       <c r="F7">
-        <v>-245.6819999999971</v>
+        <v>-245.68199999999709</v>
       </c>
       <c r="G7">
-        <v>29.46299999999974</v>
+        <v>29.462999999999742</v>
       </c>
       <c r="H7">
-        <v>-526.018</v>
+        <v>-526.01800000000003</v>
       </c>
       <c r="I7">
-        <v>32913251.7809999</v>
+        <v>32913251.780999899</v>
       </c>
       <c r="J7">
-        <v>48011316.329</v>
+        <v>48011316.329000004</v>
       </c>
       <c r="K7">
-        <v>17989835.58799982</v>
+        <v>17989835.587999821</v>
       </c>
       <c r="L7">
         <v>-32739716.58700037</v>
       </c>
       <c r="M7">
-        <v>4078201.59499979</v>
+        <v>4078201.5949997902</v>
       </c>
       <c r="N7">
-        <v>-69225665.73500013</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>-69225665.735000134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
       <c r="C8">
         <v>2422.797</v>
@@ -732,205 +799,189 @@
         <v>2717.489</v>
       </c>
       <c r="E8">
-        <v>2103.942000000001</v>
+        <v>2103.9420000000009</v>
       </c>
       <c r="F8">
         <v>2409.219000000001</v>
       </c>
       <c r="G8">
-        <v>3023.745999999999</v>
+        <v>3023.7459999999992</v>
       </c>
       <c r="H8">
         <v>1664.476999999999</v>
       </c>
       <c r="I8">
-        <v>35874282.97600001</v>
+        <v>35874282.976000011</v>
       </c>
       <c r="J8">
-        <v>40235062.609</v>
+        <v>40235062.608999997</v>
       </c>
       <c r="K8">
         <v>31092607.04700001</v>
       </c>
       <c r="L8">
-        <v>320471773.766</v>
+        <v>320471773.76599997</v>
       </c>
       <c r="M8">
-        <v>402595073.017</v>
+        <v>402595073.01700002</v>
       </c>
       <c r="N8">
-        <v>221193256.4419999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>221193256.44199991</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>1043.576999999999</v>
+        <v>1043.5769999999991</v>
       </c>
       <c r="D9">
         <v>1368.508</v>
       </c>
       <c r="E9">
-        <v>687.9649999999992</v>
+        <v>687.96499999999924</v>
       </c>
       <c r="F9">
-        <v>589.5869999999995</v>
+        <v>589.58699999999953</v>
       </c>
       <c r="G9">
-        <v>1163.380999999999</v>
+        <v>1163.3809999999989</v>
       </c>
       <c r="H9">
-        <v>-63.58899999999994</v>
+        <v>-63.588999999999942</v>
       </c>
       <c r="I9">
-        <v>15483867.37300001</v>
+        <v>15483867.373000011</v>
       </c>
       <c r="J9">
-        <v>20305123.558</v>
+        <v>20305123.557999998</v>
       </c>
       <c r="K9">
-        <v>10175059.06</v>
+        <v>10175059.060000001</v>
       </c>
       <c r="L9">
-        <v>78844980.75199986</v>
+        <v>78844980.751999855</v>
       </c>
       <c r="M9">
         <v>154000547.2510002</v>
       </c>
       <c r="N9">
-        <v>-8339660.927999973</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>-8339660.9279999733</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10">
         <v>-4065.107</v>
       </c>
       <c r="D10">
-        <v>-3484.107000000002</v>
+        <v>-3484.1070000000018</v>
       </c>
       <c r="E10">
-        <v>-4684.091</v>
+        <v>-4684.0910000000003</v>
       </c>
       <c r="F10">
-        <v>-7611.713</v>
+        <v>-7611.7129999999997</v>
       </c>
       <c r="G10">
-        <v>-6455.915000000001</v>
+        <v>-6455.9150000000009</v>
       </c>
       <c r="H10">
         <v>-8861.604000000003</v>
       </c>
       <c r="I10">
-        <v>-60208020.68200001</v>
+        <v>-60208020.682000011</v>
       </c>
       <c r="J10">
-        <v>-51552497.48800001</v>
+        <v>-51552497.488000013</v>
       </c>
       <c r="K10">
-        <v>-69432129.67099997</v>
+        <v>-69432129.670999974</v>
       </c>
       <c r="L10">
         <v>-1012141267.773</v>
       </c>
       <c r="M10">
-        <v>-859152484.2059999</v>
+        <v>-859152484.20599985</v>
       </c>
       <c r="N10">
         <v>-1178387870.658</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>461.268</v>
+        <v>461.26799999999997</v>
       </c>
       <c r="D11">
-        <v>510.0710000000001</v>
+        <v>510.07100000000008</v>
       </c>
       <c r="E11">
-        <v>408.7640000000001</v>
+        <v>408.76400000000012</v>
       </c>
       <c r="F11">
-        <v>776.0330000000004</v>
+        <v>776.03300000000036</v>
       </c>
       <c r="G11">
-        <v>869.1779999999999</v>
+        <v>869.17799999999988</v>
       </c>
       <c r="H11">
-        <v>677.5719999999997</v>
+        <v>677.57199999999966</v>
       </c>
       <c r="I11">
         <v>34686899.78199999</v>
       </c>
       <c r="J11">
-        <v>38370985.06200001</v>
+        <v>38370985.062000006</v>
       </c>
       <c r="K11">
-        <v>30702017.792</v>
+        <v>30702017.791999999</v>
       </c>
       <c r="L11">
         <v>103212085.663</v>
       </c>
       <c r="M11">
-        <v>115477503.658</v>
+        <v>115477503.65800001</v>
       </c>
       <c r="N11">
-        <v>90063074.24300003</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>90063074.243000031</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>148.8040000000001</v>
+        <v>148.80400000000009</v>
       </c>
       <c r="D12">
-        <v>216.694</v>
+        <v>216.69399999999999</v>
       </c>
       <c r="E12">
-        <v>75.67900000000009</v>
+        <v>75.679000000000087</v>
       </c>
       <c r="F12">
-        <v>169.5640000000003</v>
+        <v>169.56400000000031</v>
       </c>
       <c r="G12">
-        <v>304.0070000000001</v>
+        <v>304.00700000000012</v>
       </c>
       <c r="H12">
         <v>23.38900000000012</v>
@@ -939,139 +990,127 @@
         <v>11181823.73100001</v>
       </c>
       <c r="J12">
-        <v>16246172.48900001</v>
+        <v>16246172.489000009</v>
       </c>
       <c r="K12">
-        <v>5703051.00500001</v>
+        <v>5703051.0050000101</v>
       </c>
       <c r="L12">
-        <v>22612508.60100001</v>
+        <v>22612508.601000011</v>
       </c>
       <c r="M12">
-        <v>40283823.00199997</v>
+        <v>40283823.001999967</v>
       </c>
       <c r="N12">
-        <v>3264982.771999955</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>3264982.7719999552</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>-859.0769999999998</v>
+        <v>-859.07699999999977</v>
       </c>
       <c r="D13">
-        <v>-746.7690000000002</v>
+        <v>-746.76900000000023</v>
       </c>
       <c r="E13">
         <v>-975.54</v>
       </c>
       <c r="F13">
-        <v>-1911.745</v>
+        <v>-1911.7449999999999</v>
       </c>
       <c r="G13">
-        <v>-1666.121</v>
+        <v>-1666.1210000000001</v>
       </c>
       <c r="H13">
         <v>-2173.35</v>
       </c>
       <c r="I13">
-        <v>-64624372.449</v>
+        <v>-64624372.449000001</v>
       </c>
       <c r="J13">
-        <v>-56130368.71900001</v>
+        <v>-56130368.719000012</v>
       </c>
       <c r="K13">
-        <v>-73392910.942</v>
+        <v>-73392910.942000002</v>
       </c>
       <c r="L13">
-        <v>-254195513.51</v>
+        <v>-254195513.50999999</v>
       </c>
       <c r="M13">
         <v>-221313725.09</v>
       </c>
       <c r="N13">
-        <v>-288848928.3660001</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>-288848928.36600012</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>3044.339</v>
+        <v>3044.3389999999999</v>
       </c>
       <c r="D14">
-        <v>2989.208</v>
+        <v>2989.2080000000001</v>
       </c>
       <c r="E14">
         <v>3096.800999999999</v>
       </c>
       <c r="F14">
-        <v>4389.900000000001</v>
+        <v>4389.9000000000005</v>
       </c>
       <c r="G14">
-        <v>4385.867999999999</v>
+        <v>4385.8679999999986</v>
       </c>
       <c r="H14">
-        <v>4387.712999999999</v>
+        <v>4387.7129999999988</v>
       </c>
       <c r="I14">
-        <v>51265644.68100001</v>
+        <v>51265644.681000009</v>
       </c>
       <c r="J14">
-        <v>50319417.594</v>
+        <v>50319417.593999997</v>
       </c>
       <c r="K14">
-        <v>52150438.421</v>
+        <v>52150438.420999996</v>
       </c>
       <c r="L14">
-        <v>583722285.136</v>
+        <v>583722285.13600004</v>
       </c>
       <c r="M14">
-        <v>583639390.0679998</v>
+        <v>583639390.06799984</v>
       </c>
       <c r="N14">
         <v>583389884.0999999</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
         <v>2347.096</v>
       </c>
       <c r="D15">
-        <v>2360.909</v>
+        <v>2360.9090000000001</v>
       </c>
       <c r="E15">
         <v>2326.692</v>
       </c>
       <c r="F15">
-        <v>2780.335999999999</v>
+        <v>2780.3359999999989</v>
       </c>
       <c r="G15">
         <v>2886.152</v>
@@ -1080,16 +1119,16 @@
         <v>2667.485000000001</v>
       </c>
       <c r="I15">
-        <v>39521469.156</v>
+        <v>39521469.156000003</v>
       </c>
       <c r="J15">
-        <v>39758715.156</v>
+        <v>39758715.156000003</v>
       </c>
       <c r="K15">
-        <v>39198700.91599999</v>
+        <v>39198700.915999994</v>
       </c>
       <c r="L15">
-        <v>369736806.2399999</v>
+        <v>369736806.23999989</v>
       </c>
       <c r="M15">
         <v>383749383.898</v>
@@ -1098,82 +1137,74 @@
         <v>354487539.5259999</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
-        <v>363.1639999999998</v>
+        <v>363.16399999999982</v>
       </c>
       <c r="D16">
-        <v>484.4159999999993</v>
+        <v>484.41599999999931</v>
       </c>
       <c r="E16">
-        <v>241.8400000000001</v>
+        <v>241.84000000000009</v>
       </c>
       <c r="F16">
         <v>-77.65599999999904</v>
       </c>
       <c r="G16">
-        <v>130.4279999999999</v>
+        <v>130.42799999999991</v>
       </c>
       <c r="H16">
-        <v>-287.7090000000007</v>
+        <v>-287.70900000000069</v>
       </c>
       <c r="I16">
-        <v>6127148.941999987</v>
+        <v>6127148.9419999868</v>
       </c>
       <c r="J16">
-        <v>8120784.795000002</v>
+        <v>8120784.7950000018</v>
       </c>
       <c r="K16">
-        <v>4052198.366999999</v>
+        <v>4052198.3669999992</v>
       </c>
       <c r="L16">
-        <v>-10508388.76999998</v>
+        <v>-10508388.769999981</v>
       </c>
       <c r="M16">
-        <v>17077931.1329999</v>
+        <v>17077931.132999901</v>
       </c>
       <c r="N16">
-        <v>-38321154.09599996</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>-38321154.095999964</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>9901.088</v>
+        <v>9901.0879999999997</v>
       </c>
       <c r="D17">
         <v>10885.866</v>
       </c>
       <c r="E17">
-        <v>8844.025000000001</v>
+        <v>8844.0250000000015</v>
       </c>
       <c r="F17">
-        <v>2273.705</v>
+        <v>2273.7049999999999</v>
       </c>
       <c r="G17">
-        <v>2765.363</v>
+        <v>2765.3629999999998</v>
       </c>
       <c r="H17">
-        <v>1679.292000000001</v>
+        <v>1679.2920000000011</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,43 +1216,39 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>302353958.5869999</v>
+        <v>302353958.58699989</v>
       </c>
       <c r="M17">
-        <v>368030554.135</v>
+        <v>368030554.13499999</v>
       </c>
       <c r="N17">
         <v>222981343.7490001</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>4096.823</v>
+        <v>4096.8230000000003</v>
       </c>
       <c r="D18">
-        <v>5076.526999999998</v>
+        <v>5076.5269999999982</v>
       </c>
       <c r="E18">
-        <v>3106.748000000003</v>
+        <v>3106.7480000000028</v>
       </c>
       <c r="F18">
-        <v>650.9430000000011</v>
+        <v>650.94300000000112</v>
       </c>
       <c r="G18">
-        <v>1035.459</v>
+        <v>1035.4590000000001</v>
       </c>
       <c r="H18">
-        <v>246.8220000000001</v>
+        <v>246.82200000000009</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1236,22 +1263,18 @@
         <v>86452883.36800015</v>
       </c>
       <c r="M18">
-        <v>137799441.723</v>
+        <v>137799441.72299999</v>
       </c>
       <c r="N18">
         <v>32453154.32400012</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
       </c>
       <c r="C19">
         <v>-15576.306</v>
@@ -1263,13 +1286,13 @@
         <v>-17525.03000000001</v>
       </c>
       <c r="F19">
-        <v>-6024.174999999999</v>
+        <v>-6024.1749999999993</v>
       </c>
       <c r="G19">
-        <v>-5175.860000000001</v>
+        <v>-5175.8600000000006</v>
       </c>
       <c r="H19">
-        <v>-6904.485000000001</v>
+        <v>-6904.4850000000006</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,94 +1304,86 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>-801578852.099</v>
+        <v>-801578852.09899998</v>
       </c>
       <c r="M19">
-        <v>-688313943.072</v>
+        <v>-688313943.07200003</v>
       </c>
       <c r="N19">
-        <v>-919296434.0240002</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>-919296434.02400017</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>-598.7330000000002</v>
+        <v>-598.73300000000017</v>
       </c>
       <c r="D20">
-        <v>601.8899999999994</v>
+        <v>601.88999999999942</v>
       </c>
       <c r="E20">
         <v>-1892.183999999987</v>
       </c>
       <c r="F20">
-        <v>-4612.906999999999</v>
+        <v>-4612.9069999999992</v>
       </c>
       <c r="G20">
         <v>-2268.788</v>
       </c>
       <c r="H20">
-        <v>-7260.716</v>
+        <v>-7260.7160000000003</v>
       </c>
       <c r="I20">
-        <v>-8849870.332999945</v>
+        <v>-8849870.3329999447</v>
       </c>
       <c r="J20">
         <v>8987688.67900002</v>
       </c>
       <c r="K20">
-        <v>-28164463.56399995</v>
+        <v>-28164463.563999951</v>
       </c>
       <c r="L20">
-        <v>-612824513.2550001</v>
+        <v>-612824513.25500011</v>
       </c>
       <c r="M20">
-        <v>-302556863.9379997</v>
+        <v>-302556863.93799973</v>
       </c>
       <c r="N20">
         <v>-965534275.1439991</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>14558.12499999999</v>
+        <v>14558.124999999991</v>
       </c>
       <c r="D21">
         <v>14895.18300000001</v>
       </c>
       <c r="E21">
-        <v>14216.851</v>
+        <v>14216.851000000001</v>
       </c>
       <c r="F21">
-        <v>10103.74200000001</v>
+        <v>10103.742000000009</v>
       </c>
       <c r="G21">
-        <v>10568.551</v>
+        <v>10568.550999999999</v>
       </c>
       <c r="H21">
-        <v>9617.718000000001</v>
+        <v>9617.7180000000008</v>
       </c>
       <c r="I21">
-        <v>810839207.2690001</v>
+        <v>810839207.26900005</v>
       </c>
       <c r="J21">
         <v>829793990.0619998</v>
@@ -1377,7 +1392,7 @@
         <v>791567715.1239996</v>
       </c>
       <c r="L21">
-        <v>1343504893.412001</v>
+        <v>1343504893.4120009</v>
       </c>
       <c r="M21">
         <v>1405890790.848999</v>
@@ -1386,64 +1401,56 @@
         <v>1279559083.365999</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>5754.599</v>
+        <v>5754.5990000000002</v>
       </c>
       <c r="D22">
-        <v>5834.532999999999</v>
+        <v>5834.5329999999994</v>
       </c>
       <c r="E22">
-        <v>5665.332999999999</v>
+        <v>5665.3329999999987</v>
       </c>
       <c r="F22">
-        <v>7092.580000000002</v>
+        <v>7092.5800000000017</v>
       </c>
       <c r="G22">
-        <v>7402.448</v>
+        <v>7402.4480000000003</v>
       </c>
       <c r="H22">
-        <v>6767.488999999998</v>
+        <v>6767.4889999999978</v>
       </c>
       <c r="I22">
-        <v>96914262.77900001</v>
+        <v>96914262.779000014</v>
       </c>
       <c r="J22">
-        <v>98198917.54500002</v>
+        <v>98198917.545000017</v>
       </c>
       <c r="K22">
-        <v>95401337.70400003</v>
+        <v>95401337.704000026</v>
       </c>
       <c r="L22">
-        <v>942950702.6059999</v>
+        <v>942950702.60599995</v>
       </c>
       <c r="M22">
-        <v>984466705.099</v>
+        <v>984466705.09899998</v>
       </c>
       <c r="N22">
-        <v>899556269.5299997</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>899556269.52999973</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
       </c>
       <c r="C23">
         <v>-1578.39499999999</v>
@@ -1452,16 +1459,16 @@
         <v>2305.51999999999</v>
       </c>
       <c r="E23">
-        <v>-5574.256999999983</v>
+        <v>-5574.2569999999832</v>
       </c>
       <c r="F23">
-        <v>-3099.527000000002</v>
+        <v>-3099.5270000000019</v>
       </c>
       <c r="G23">
         <v>-1375.038</v>
       </c>
       <c r="H23">
-        <v>-4978.370999999999</v>
+        <v>-4978.3709999999992</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1476,88 +1483,80 @@
         <v>-412772010.1439991</v>
       </c>
       <c r="M23">
-        <v>-182483947.2139997</v>
+        <v>-182483947.21399969</v>
       </c>
       <c r="N23">
-        <v>-663861935.9509993</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>-663861935.95099926</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>-249.005000000001</v>
+        <v>-249.00500000000099</v>
       </c>
       <c r="D24">
-        <v>-20.00400000000081</v>
+        <v>-20.004000000000811</v>
       </c>
       <c r="E24">
-        <v>-491.0969999999988</v>
+        <v>-491.09699999999879</v>
       </c>
       <c r="F24">
-        <v>-966.1479999999992</v>
+        <v>-966.14799999999923</v>
       </c>
       <c r="G24">
-        <v>-492.9359999999997</v>
+        <v>-492.93599999999969</v>
       </c>
       <c r="H24">
         <v>-1472.388999999999</v>
       </c>
       <c r="I24">
-        <v>-18755648.93600005</v>
+        <v>-18755648.936000049</v>
       </c>
       <c r="J24">
-        <v>-1513211.167999983</v>
+        <v>-1513211.1679999831</v>
       </c>
       <c r="K24">
-        <v>-36987842.14500004</v>
+        <v>-36987842.145000041</v>
       </c>
       <c r="L24">
         <v>-128370919.2460001</v>
       </c>
       <c r="M24">
-        <v>-65552398.43000007</v>
+        <v>-65552398.430000067</v>
       </c>
       <c r="N24">
         <v>-195520871.3510001</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>41306.08899999999</v>
+        <v>41306.088999999993</v>
       </c>
       <c r="D25">
-        <v>39949.934</v>
+        <v>39949.934000000001</v>
       </c>
       <c r="E25">
-        <v>42656.641</v>
+        <v>42656.641000000003</v>
       </c>
       <c r="F25">
-        <v>370423.1830000002</v>
+        <v>370423.18300000019</v>
       </c>
       <c r="G25">
-        <v>367273.3040000001</v>
+        <v>367273.30400000012</v>
       </c>
       <c r="H25">
-        <v>373500.5820000001</v>
+        <v>373500.58200000011</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1569,28 +1568,24 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>49268072625.20001</v>
+        <v>49268072625.200012</v>
       </c>
       <c r="M25">
-        <v>48845991701.00999</v>
+        <v>48845991701.009987</v>
       </c>
       <c r="N25">
         <v>49679111585.875</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>40631.32900000001</v>
+        <v>40631.329000000012</v>
       </c>
       <c r="D26">
         <v>41191.27900000001</v>
@@ -1599,226 +1594,211 @@
         <v>39969.97099999999</v>
       </c>
       <c r="F26">
-        <v>168637.843</v>
+        <v>168637.84299999999</v>
       </c>
       <c r="G26">
-        <v>167101.504</v>
+        <v>167101.50399999999</v>
       </c>
       <c r="H26">
-        <v>169880.371</v>
+        <v>169880.37100000001</v>
       </c>
       <c r="I26">
         <v>570252554.255</v>
       </c>
       <c r="J26">
-        <v>574343220.873</v>
+        <v>574343220.87300003</v>
       </c>
       <c r="K26">
-        <v>565189628.2079999</v>
+        <v>565189628.20799994</v>
       </c>
       <c r="L26">
-        <v>22427095456.58001</v>
+        <v>22427095456.580009</v>
       </c>
       <c r="M26">
-        <v>22229968892.318</v>
+        <v>22229968892.318001</v>
       </c>
       <c r="N26">
-        <v>22591907563.27101</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>22591907563.271011</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>30023.82999999999</v>
+        <v>30023.829999999991</v>
       </c>
       <c r="D27">
         <v>30984.24400000001</v>
       </c>
       <c r="E27">
-        <v>28996.887</v>
+        <v>28996.886999999999</v>
       </c>
       <c r="F27">
         <v>149993.495</v>
       </c>
       <c r="G27">
-        <v>150604.347</v>
+        <v>150604.34700000001</v>
       </c>
       <c r="H27">
         <v>149212.7000000001</v>
       </c>
       <c r="I27">
-        <v>395687388.932</v>
+        <v>395687388.93199998</v>
       </c>
       <c r="J27">
-        <v>412674929.3280001</v>
+        <v>412674929.32800013</v>
       </c>
       <c r="K27">
-        <v>377410125.5690001</v>
+        <v>377410125.56900012</v>
       </c>
       <c r="L27">
-        <v>19949807496.519</v>
+        <v>19949807496.519001</v>
       </c>
       <c r="M27">
-        <v>20030299351.56499</v>
+        <v>20030299351.564991</v>
       </c>
       <c r="N27">
-        <v>19847513956.017</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>19847513956.016998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
       </c>
       <c r="C28">
         <v>-11462.47900000001</v>
       </c>
       <c r="D28">
-        <v>-8608.467000000004</v>
+        <v>-8608.4670000000042</v>
       </c>
       <c r="E28">
         <v>-14385.571</v>
       </c>
       <c r="F28">
-        <v>60309.5849999999</v>
+        <v>60309.584999999897</v>
       </c>
       <c r="G28">
-        <v>63401.68999999994</v>
+        <v>63401.689999999937</v>
       </c>
       <c r="H28">
-        <v>57081.24200000014</v>
+        <v>57081.242000000137</v>
       </c>
       <c r="I28">
-        <v>-85791992.40799999</v>
+        <v>-85791992.407999992</v>
       </c>
       <c r="J28">
-        <v>-51550765.08299994</v>
+        <v>-51550765.082999937</v>
       </c>
       <c r="K28">
-        <v>-120783006.658</v>
+        <v>-120783006.65800001</v>
       </c>
       <c r="L28">
         <v>8023657825.473999</v>
       </c>
       <c r="M28">
-        <v>8425487743.492996</v>
+        <v>8425487743.4929962</v>
       </c>
       <c r="N28">
-        <v>7593888337.03701</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>7593888337.0370102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
       </c>
       <c r="C29">
-        <v>59192.67999999999</v>
+        <v>59192.679999999993</v>
       </c>
       <c r="D29">
-        <v>63567.05599999998</v>
+        <v>63567.055999999982</v>
       </c>
       <c r="E29">
-        <v>54581.28699999989</v>
+        <v>54581.286999999887</v>
       </c>
       <c r="F29">
-        <v>378940.9230000001</v>
+        <v>378940.92300000013</v>
       </c>
       <c r="G29">
-        <v>381107.5409999999</v>
+        <v>381107.54099999991</v>
       </c>
       <c r="H29">
-        <v>376174.313</v>
+        <v>376174.31300000002</v>
       </c>
       <c r="I29">
-        <v>880147950.7789998</v>
+        <v>880147950.77899981</v>
       </c>
       <c r="J29">
-        <v>935467385.118</v>
+        <v>935467385.11800003</v>
       </c>
       <c r="K29">
-        <v>821816747.1190004</v>
+        <v>821816747.11900043</v>
       </c>
       <c r="L29">
-        <v>50400560778.573</v>
+        <v>50400560778.572998</v>
       </c>
       <c r="M29">
-        <v>50685755987.37599</v>
+        <v>50685755987.375992</v>
       </c>
       <c r="N29">
-        <v>50033309856.3251</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>50033309856.325104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
       </c>
       <c r="C30">
-        <v>17886.59100000001</v>
+        <v>17886.591000000011</v>
       </c>
       <c r="D30">
-        <v>23617.122</v>
+        <v>23617.121999999999</v>
       </c>
       <c r="E30">
-        <v>11924.64599999998</v>
+        <v>11924.645999999981</v>
       </c>
       <c r="F30">
-        <v>8517.739999999991</v>
+        <v>8517.7399999999907</v>
       </c>
       <c r="G30">
-        <v>13834.23700000002</v>
+        <v>13834.237000000019</v>
       </c>
       <c r="H30">
-        <v>2673.730999999883</v>
+        <v>2673.7309999998829</v>
       </c>
       <c r="I30">
-        <v>880147950.7789998</v>
+        <v>880147950.77899981</v>
       </c>
       <c r="J30">
-        <v>935467385.118</v>
+        <v>935467385.11800003</v>
       </c>
       <c r="K30">
-        <v>821816747.1190004</v>
+        <v>821816747.11900043</v>
       </c>
       <c r="L30">
         <v>1132488153.372997</v>
       </c>
       <c r="M30">
-        <v>1839764286.365997</v>
+        <v>1839764286.3659971</v>
       </c>
       <c r="N30">
-        <v>354198270.4500008</v>
+        <v>354198270.45000082</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N30" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
@@ -1,123 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C40D54-6B55-EF4F-9E29-BD9F9FC360DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="24680" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$30</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>area_type</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>periurban</t>
-  </si>
-  <si>
-    <t>rural</t>
-  </si>
-  <si>
-    <t>urban</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -217,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -251,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -286,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -462,89 +350,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>area_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C2">
-        <v>16752.394</v>
+        <v>19509.293</v>
       </c>
       <c r="D2">
-        <v>16094.655000000001</v>
+        <v>18673.639</v>
       </c>
       <c r="E2">
-        <v>17411.444</v>
+        <v>20342.699</v>
       </c>
       <c r="F2">
-        <v>152575.07999999999</v>
+        <v>185393.338</v>
       </c>
       <c r="G2">
-        <v>149843.095</v>
+        <v>181100.034</v>
       </c>
       <c r="H2">
-        <v>155261.519</v>
+        <v>189629.224</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -556,39 +465,43 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>20290908039.326</v>
+        <v>24656879688.883</v>
       </c>
       <c r="M2">
-        <v>19933286637.138</v>
+        <v>24089737440.448</v>
       </c>
       <c r="N2">
-        <v>20648620987.93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
+        <v>25225865688.877</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C3">
-        <v>16471.484</v>
+        <v>18845.975</v>
       </c>
       <c r="D3">
-        <v>15924.705</v>
+        <v>18147.743</v>
       </c>
       <c r="E3">
-        <v>17010.27</v>
+        <v>19536.427</v>
       </c>
       <c r="F3">
-        <v>141667.54699999999</v>
+        <v>177400.037</v>
       </c>
       <c r="G3">
-        <v>140890.514</v>
+        <v>174718.727</v>
       </c>
       <c r="H3">
-        <v>142404.655</v>
+        <v>180027.821</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -600,39 +513,43 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>18842343021.660999</v>
+        <v>23591860969.302</v>
       </c>
       <c r="M3">
-        <v>18739593300.738998</v>
+        <v>23240531183.743</v>
       </c>
       <c r="N3">
-        <v>18942522208.028999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
+        <v>23946733077.677</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C4">
-        <v>8082.2109999999993</v>
+        <v>13644.22</v>
       </c>
       <c r="D4">
-        <v>7930.5740000000014</v>
+        <v>13163.121</v>
       </c>
       <c r="E4">
-        <v>8234.926999999996</v>
+        <v>14126.472</v>
       </c>
       <c r="F4">
-        <v>76180.555999999982</v>
+        <v>143802.068</v>
       </c>
       <c r="G4">
-        <v>76539.695000000007</v>
+        <v>141537.71</v>
       </c>
       <c r="H4">
-        <v>75834.408000000054</v>
+        <v>146083.48</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -644,567 +561,619 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>10134821564.213011</v>
+        <v>19129725246.076</v>
       </c>
       <c r="M4">
-        <v>10173111763.132999</v>
+        <v>18823664147.268</v>
       </c>
       <c r="N4">
-        <v>10087968389.916</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
+        <v>19432909804.761</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C5">
-        <v>8049.4429999999993</v>
+        <v>12225</v>
       </c>
       <c r="D5">
-        <v>7993.989999999998</v>
+        <v>11899.494</v>
       </c>
       <c r="E5">
-        <v>8104.9950000000008</v>
+        <v>12547.213</v>
       </c>
       <c r="F5">
-        <v>6213.9060000000009</v>
+        <v>9997.686000000002</v>
       </c>
       <c r="G5">
-        <v>6214.2540000000008</v>
+        <v>9766.778999999999</v>
       </c>
       <c r="H5">
-        <v>6209.7979999999989</v>
+        <v>10226.117</v>
       </c>
       <c r="I5">
-        <v>448425726.81599998</v>
+        <v>680972788.5039999</v>
       </c>
       <c r="J5">
-        <v>445417755.60799992</v>
+        <v>662904568.6479999</v>
       </c>
       <c r="K5">
-        <v>451244564.94800001</v>
+        <v>699128508.6719999</v>
       </c>
       <c r="L5">
-        <v>826427314.102</v>
+        <v>1329844702.133</v>
       </c>
       <c r="M5">
-        <v>826939734.30200005</v>
+        <v>1299295319.196</v>
       </c>
       <c r="N5">
-        <v>825659016.80699992</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
+        <v>1359679294.553</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C6">
-        <v>5916.0460000000003</v>
+        <v>9591.328000000001</v>
       </c>
       <c r="D6">
-        <v>6036.9009999999998</v>
+        <v>9425.666999999999</v>
       </c>
       <c r="E6">
-        <v>5789.5330000000013</v>
+        <v>9757.661999999998</v>
       </c>
       <c r="F6">
-        <v>4135.518</v>
+        <v>7880.279</v>
       </c>
       <c r="G6">
-        <v>4324.8339999999998</v>
+        <v>7781.686999999999</v>
       </c>
       <c r="H6">
-        <v>3933.9379999999978</v>
+        <v>7976.136999999999</v>
       </c>
       <c r="I6">
-        <v>329500228.67199987</v>
+        <v>534258104.704</v>
       </c>
       <c r="J6">
-        <v>336364918.12499988</v>
+        <v>524762567.073</v>
       </c>
       <c r="K6">
-        <v>322333314.58799988</v>
+        <v>543478008.558</v>
       </c>
       <c r="L6">
-        <v>549817295.89700007</v>
+        <v>1048270659.398</v>
       </c>
       <c r="M6">
-        <v>574872854.95200002</v>
+        <v>1034255717.377</v>
       </c>
       <c r="N6">
-        <v>523125732.29399991</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
+        <v>1060515870.668</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C7">
-        <v>592.6359999999986</v>
+        <v>8302.130000000001</v>
       </c>
       <c r="D7">
-        <v>864.29200000000128</v>
+        <v>8149.454000000002</v>
       </c>
       <c r="E7">
-        <v>322.32299999999668</v>
+        <v>8454.790999999997</v>
       </c>
       <c r="F7">
-        <v>-245.68199999999709</v>
+        <v>7338.808000000001</v>
       </c>
       <c r="G7">
-        <v>29.462999999999742</v>
+        <v>7230.684000000001</v>
       </c>
       <c r="H7">
-        <v>-526.01800000000003</v>
+        <v>7445.133999999998</v>
       </c>
       <c r="I7">
-        <v>32913251.780999899</v>
+        <v>462535922.313</v>
       </c>
       <c r="J7">
-        <v>48011316.329000004</v>
+        <v>453841101.9229999</v>
       </c>
       <c r="K7">
-        <v>17989835.587999821</v>
+        <v>471174495.0739999</v>
       </c>
       <c r="L7">
-        <v>-32739716.58700037</v>
+        <v>975824629.3649998</v>
       </c>
       <c r="M7">
-        <v>4078201.5949997902</v>
+        <v>962000053.302</v>
       </c>
       <c r="N7">
-        <v>-69225665.735000134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>989878200.4769998</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C8">
-        <v>2422.797</v>
+        <v>5795.068</v>
       </c>
       <c r="D8">
-        <v>2717.489</v>
+        <v>5798.173</v>
       </c>
       <c r="E8">
-        <v>2103.9420000000009</v>
+        <v>5777.031000000001</v>
       </c>
       <c r="F8">
-        <v>2409.219000000001</v>
+        <v>7315.199000000001</v>
       </c>
       <c r="G8">
-        <v>3023.7459999999992</v>
+        <v>7346.737999999999</v>
       </c>
       <c r="H8">
-        <v>1664.476999999999</v>
+        <v>7225.523000000001</v>
       </c>
       <c r="I8">
-        <v>35874282.976000011</v>
+        <v>85813551.79699999</v>
       </c>
       <c r="J8">
-        <v>40235062.608999997</v>
+        <v>85825047.37899998</v>
       </c>
       <c r="K8">
-        <v>31092607.04700001</v>
+        <v>85454810.846</v>
       </c>
       <c r="L8">
-        <v>320471773.76599997</v>
+        <v>973034696.424</v>
       </c>
       <c r="M8">
-        <v>402595073.01700002</v>
+        <v>977361583.5149999</v>
       </c>
       <c r="N8">
-        <v>221193256.44199991</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
+        <v>961224868.7600002</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C9">
-        <v>1043.5769999999991</v>
+        <v>4090.767</v>
       </c>
       <c r="D9">
-        <v>1368.508</v>
+        <v>4125.324000000001</v>
       </c>
       <c r="E9">
-        <v>687.96499999999924</v>
+        <v>4042.592</v>
       </c>
       <c r="F9">
-        <v>589.58699999999953</v>
+        <v>5232.619000000001</v>
       </c>
       <c r="G9">
-        <v>1163.3809999999989</v>
+        <v>5287.691999999999</v>
       </c>
       <c r="H9">
-        <v>-63.588999999999942</v>
+        <v>5130.632</v>
       </c>
       <c r="I9">
-        <v>15483867.373000011</v>
+        <v>60606967.63300002</v>
       </c>
       <c r="J9">
-        <v>20305123.557999998</v>
+        <v>61105518.92799999</v>
       </c>
       <c r="K9">
-        <v>10175059.060000001</v>
+        <v>59888950.206</v>
       </c>
       <c r="L9">
-        <v>78844980.751999855</v>
+        <v>696415583.0639999</v>
       </c>
       <c r="M9">
-        <v>154000547.2510002</v>
+        <v>702724229.803</v>
       </c>
       <c r="N9">
-        <v>-8339660.9279999733</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
+        <v>683469851.3280001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C10">
-        <v>-4065.107</v>
+        <v>3917.314999999999</v>
       </c>
       <c r="D10">
-        <v>-3484.1070000000018</v>
+        <v>3982.407999999999</v>
       </c>
       <c r="E10">
-        <v>-4684.0910000000003</v>
+        <v>3825.474000000002</v>
       </c>
       <c r="F10">
-        <v>-7611.7129999999997</v>
+        <v>5603.216</v>
       </c>
       <c r="G10">
-        <v>-6455.9150000000009</v>
+        <v>5737.771000000001</v>
       </c>
       <c r="H10">
-        <v>-8861.604000000003</v>
+        <v>5411.445999999996</v>
       </c>
       <c r="I10">
-        <v>-60208020.682000011</v>
+        <v>57967787.46099997</v>
       </c>
       <c r="J10">
-        <v>-51552497.488000013</v>
+        <v>59018929.58500001</v>
       </c>
       <c r="K10">
-        <v>-69432129.670999974</v>
+        <v>56623329.31100002</v>
       </c>
       <c r="L10">
-        <v>-1012141267.773</v>
+        <v>745123278.0799999</v>
       </c>
       <c r="M10">
-        <v>-859152484.20599985</v>
+        <v>763131959.8800001</v>
       </c>
       <c r="N10">
-        <v>-1178387870.658</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
+        <v>718669294.7290001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C11">
-        <v>461.26799999999997</v>
+        <v>1342.347</v>
       </c>
       <c r="D11">
-        <v>510.07100000000008</v>
+        <v>1335.412</v>
       </c>
       <c r="E11">
-        <v>408.76400000000012</v>
+        <v>1344.993</v>
       </c>
       <c r="F11">
-        <v>776.03300000000036</v>
+        <v>2354.626</v>
       </c>
       <c r="G11">
-        <v>869.17799999999988</v>
+        <v>2342.195999999999</v>
       </c>
       <c r="H11">
-        <v>677.57199999999966</v>
+        <v>2363.049</v>
       </c>
       <c r="I11">
-        <v>34686899.78199999</v>
+        <v>100938754.207</v>
       </c>
       <c r="J11">
-        <v>38370985.062000006</v>
+        <v>100471617.177</v>
       </c>
       <c r="K11">
-        <v>30702017.791999999</v>
+        <v>101189032.547</v>
       </c>
       <c r="L11">
-        <v>103212085.663</v>
+        <v>313182030.589</v>
       </c>
       <c r="M11">
-        <v>115477503.65800001</v>
+        <v>311509148.828</v>
       </c>
       <c r="N11">
-        <v>90063074.243000031</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
+        <v>314104775.193</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C12">
-        <v>148.80400000000009</v>
+        <v>968.4570000000001</v>
       </c>
       <c r="D12">
-        <v>216.69399999999999</v>
+        <v>972.5599999999999</v>
       </c>
       <c r="E12">
-        <v>75.679000000000087</v>
+        <v>959.442</v>
       </c>
       <c r="F12">
-        <v>169.56400000000031</v>
+        <v>1719.321</v>
       </c>
       <c r="G12">
-        <v>304.00700000000012</v>
+        <v>1729.978000000001</v>
       </c>
       <c r="H12">
-        <v>23.38900000000012</v>
+        <v>1703.296</v>
       </c>
       <c r="I12">
-        <v>11181823.73100001</v>
+        <v>72803132.08399999</v>
       </c>
       <c r="J12">
-        <v>16246172.489000009</v>
+        <v>73137005.20199999</v>
       </c>
       <c r="K12">
-        <v>5703051.0050000101</v>
+        <v>72269620.84899999</v>
       </c>
       <c r="L12">
-        <v>22612508.601000011</v>
+        <v>228738049.385</v>
       </c>
       <c r="M12">
-        <v>40283823.001999967</v>
+        <v>229848161.783</v>
       </c>
       <c r="N12">
-        <v>3264982.7719999552</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
+        <v>226438866.685</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C13">
-        <v>-859.07699999999977</v>
+        <v>1039.965</v>
       </c>
       <c r="D13">
-        <v>-746.76900000000023</v>
+        <v>1051.905999999999</v>
       </c>
       <c r="E13">
-        <v>-975.54</v>
+        <v>1025.278</v>
       </c>
       <c r="F13">
-        <v>-1911.7449999999999</v>
+        <v>2037.393</v>
       </c>
       <c r="G13">
-        <v>-1666.1210000000001</v>
+        <v>2066.195</v>
       </c>
       <c r="H13">
-        <v>-2173.35</v>
+        <v>2001.955000000001</v>
       </c>
       <c r="I13">
-        <v>-64624372.449000001</v>
+        <v>78217742.23600003</v>
       </c>
       <c r="J13">
-        <v>-56130368.719000012</v>
+        <v>79250134.38800001</v>
       </c>
       <c r="K13">
-        <v>-73392910.942000002</v>
+        <v>77094655.5</v>
       </c>
       <c r="L13">
-        <v>-254195513.50999999</v>
+        <v>271034234.5949999</v>
       </c>
       <c r="M13">
-        <v>-221313725.09</v>
+        <v>274825585.2980001</v>
       </c>
       <c r="N13">
-        <v>-288848928.36600012</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
+        <v>266337777.7189999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C14">
-        <v>3044.3389999999999</v>
+        <v>4184.805</v>
       </c>
       <c r="D14">
-        <v>2989.2080000000001</v>
+        <v>4031.041</v>
       </c>
       <c r="E14">
-        <v>3096.800999999999</v>
+        <v>4339.503</v>
       </c>
       <c r="F14">
-        <v>4389.9000000000005</v>
+        <v>6568.551</v>
       </c>
       <c r="G14">
-        <v>4385.8679999999986</v>
+        <v>6387.679999999999</v>
       </c>
       <c r="H14">
-        <v>4387.7129999999988</v>
+        <v>6746.357999999999</v>
       </c>
       <c r="I14">
-        <v>51265644.681000009</v>
+        <v>70481394.08700001</v>
       </c>
       <c r="J14">
-        <v>50319417.593999997</v>
+        <v>67901362.92400001</v>
       </c>
       <c r="K14">
-        <v>52150438.420999996</v>
+        <v>73072534.55700001</v>
       </c>
       <c r="L14">
-        <v>583722285.13600004</v>
+        <v>873354560.8449999</v>
       </c>
       <c r="M14">
-        <v>583639390.06799984</v>
+        <v>849336922.263</v>
       </c>
       <c r="N14">
-        <v>583389884.0999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
+        <v>897261840.9779999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C15">
-        <v>2347.096</v>
+        <v>3292.027</v>
       </c>
       <c r="D15">
-        <v>2360.9090000000001</v>
+        <v>3194.351</v>
       </c>
       <c r="E15">
-        <v>2326.692</v>
+        <v>3387.144</v>
       </c>
       <c r="F15">
-        <v>2780.3359999999989</v>
+        <v>4836.26</v>
       </c>
       <c r="G15">
-        <v>2886.152</v>
+        <v>4756.254</v>
       </c>
       <c r="H15">
-        <v>2667.485000000001</v>
+        <v>4914.467000000001</v>
       </c>
       <c r="I15">
-        <v>39521469.156000003</v>
+        <v>55422453.341</v>
       </c>
       <c r="J15">
-        <v>39758715.156000003</v>
+        <v>53781247.521</v>
       </c>
       <c r="K15">
-        <v>39198700.915999994</v>
+        <v>57044911.551</v>
       </c>
       <c r="L15">
-        <v>369736806.23999989</v>
+        <v>643168586.6019999</v>
       </c>
       <c r="M15">
-        <v>383749383.898</v>
+        <v>632323333.9690001</v>
       </c>
       <c r="N15">
-        <v>354487539.5259999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
+        <v>653680524.081</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C16">
-        <v>363.16399999999982</v>
+        <v>2713.578</v>
       </c>
       <c r="D16">
-        <v>484.41599999999931</v>
+        <v>2639.012</v>
       </c>
       <c r="E16">
-        <v>241.84000000000009</v>
+        <v>2789.115000000001</v>
       </c>
       <c r="F16">
-        <v>-77.65599999999904</v>
+        <v>4299.263000000001</v>
       </c>
       <c r="G16">
-        <v>130.42799999999991</v>
+        <v>4219.875</v>
       </c>
       <c r="H16">
-        <v>-287.70900000000069</v>
+        <v>4382.736000000001</v>
       </c>
       <c r="I16">
-        <v>6127148.9419999868</v>
+        <v>45707178.27199998</v>
       </c>
       <c r="J16">
-        <v>8120784.7950000018</v>
+        <v>44444321.042</v>
       </c>
       <c r="K16">
-        <v>4052198.3669999992</v>
+        <v>46905429.867</v>
       </c>
       <c r="L16">
-        <v>-10508388.769999981</v>
+        <v>571812686.0380001</v>
       </c>
       <c r="M16">
-        <v>17077931.132999901</v>
+        <v>561272100.263</v>
       </c>
       <c r="N16">
-        <v>-38321154.095999964</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
+        <v>582756223.2029998</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C17">
-        <v>9901.0879999999997</v>
+        <v>30257.585</v>
       </c>
       <c r="D17">
-        <v>10885.866</v>
+        <v>29657.554</v>
       </c>
       <c r="E17">
-        <v>8844.0250000000015</v>
+        <v>30805.107</v>
       </c>
       <c r="F17">
-        <v>2273.7049999999999</v>
+        <v>8402.962</v>
       </c>
       <c r="G17">
-        <v>2765.3629999999998</v>
+        <v>8161.563999999999</v>
       </c>
       <c r="H17">
-        <v>1679.2920000000011</v>
+        <v>8598.375000000002</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1216,39 +1185,43 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>302353958.58699989</v>
+        <v>1117761026.439</v>
       </c>
       <c r="M17">
-        <v>368030554.13499999</v>
+        <v>1085110887.154</v>
       </c>
       <c r="N17">
-        <v>222981343.7490001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
+        <v>1142093011.219</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C18">
-        <v>4096.8230000000003</v>
+        <v>21891.021</v>
       </c>
       <c r="D18">
-        <v>5076.5269999999982</v>
+        <v>21558.295</v>
       </c>
       <c r="E18">
-        <v>3106.7480000000028</v>
+        <v>22196.777</v>
       </c>
       <c r="F18">
-        <v>650.94300000000112</v>
+        <v>6088.416999999999</v>
       </c>
       <c r="G18">
-        <v>1035.4590000000001</v>
+        <v>5956.425</v>
       </c>
       <c r="H18">
-        <v>246.82200000000009</v>
+        <v>6210.381000000001</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1260,39 +1233,43 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>86452883.36800015</v>
+        <v>809768480.8090001</v>
       </c>
       <c r="M18">
-        <v>137799441.72299999</v>
+        <v>793081378.835</v>
       </c>
       <c r="N18">
-        <v>32453154.32400012</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
+        <v>825725171.5190001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C19">
-        <v>-15576.306</v>
+        <v>31507.38799999999</v>
       </c>
       <c r="D19">
-        <v>-13656.873</v>
+        <v>30962.791</v>
       </c>
       <c r="E19">
-        <v>-17525.03000000001</v>
+        <v>32024.993</v>
       </c>
       <c r="F19">
-        <v>-6024.1749999999993</v>
+        <v>10096.279</v>
       </c>
       <c r="G19">
-        <v>-5175.8600000000006</v>
+        <v>9853.644999999997</v>
       </c>
       <c r="H19">
-        <v>-6904.4850000000006</v>
+        <v>10332.617</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1304,171 +1281,187 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>-801578852.09899998</v>
+        <v>1342758615.6</v>
       </c>
       <c r="M19">
-        <v>-688313943.07200003</v>
+        <v>1312426403.634</v>
       </c>
       <c r="N19">
-        <v>-919296434.02400017</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
+        <v>1372926447.717</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C20">
-        <v>-598.73300000000017</v>
+        <v>13803.15</v>
       </c>
       <c r="D20">
-        <v>601.88999999999942</v>
+        <v>13905.905</v>
       </c>
       <c r="E20">
-        <v>-1892.183999999987</v>
+        <v>13645.09700000002</v>
       </c>
       <c r="F20">
-        <v>-4612.9069999999992</v>
+        <v>18151.034</v>
       </c>
       <c r="G20">
-        <v>-2268.788</v>
+        <v>18372.201</v>
       </c>
       <c r="H20">
-        <v>-7260.7160000000003</v>
+        <v>17767.601</v>
       </c>
       <c r="I20">
-        <v>-8849870.3329999447</v>
+        <v>204388306.891</v>
       </c>
       <c r="J20">
-        <v>8987688.67900002</v>
+        <v>205949495.892</v>
       </c>
       <c r="K20">
-        <v>-28164463.563999951</v>
+        <v>201967090.3630001</v>
       </c>
       <c r="L20">
-        <v>-612824513.25500011</v>
+        <v>2414573557.567999</v>
       </c>
       <c r="M20">
-        <v>-302556863.93799973</v>
+        <v>2443217773.198</v>
       </c>
       <c r="N20">
-        <v>-965534275.1439991</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
+        <v>2363364014.816999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C21">
-        <v>14558.124999999991</v>
+        <v>30118.45800000001</v>
       </c>
       <c r="D21">
-        <v>14895.18300000001</v>
+        <v>29474.61500000001</v>
       </c>
       <c r="E21">
-        <v>14216.851000000001</v>
+        <v>30759.666</v>
       </c>
       <c r="F21">
-        <v>10103.742000000009</v>
+        <v>25216.77300000001</v>
       </c>
       <c r="G21">
-        <v>10568.550999999999</v>
+        <v>24779.15</v>
       </c>
       <c r="H21">
-        <v>9617.7180000000008</v>
+        <v>25647.388</v>
       </c>
       <c r="I21">
-        <v>810839207.26900005</v>
+        <v>1677766815.521</v>
       </c>
       <c r="J21">
-        <v>829793990.0619998</v>
+        <v>1641508237.644</v>
       </c>
       <c r="K21">
-        <v>791567715.1239996</v>
+        <v>1713781012.304</v>
       </c>
       <c r="L21">
-        <v>1343504893.4120009</v>
+        <v>3353939990.896</v>
       </c>
       <c r="M21">
-        <v>1405890790.848999</v>
+        <v>3295551089.875</v>
       </c>
       <c r="N21">
-        <v>1279559083.365999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
+        <v>3410073365.698</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C22">
-        <v>5754.5990000000002</v>
+        <v>10190.41</v>
       </c>
       <c r="D22">
-        <v>5834.5329999999994</v>
+        <v>9864.404000000002</v>
       </c>
       <c r="E22">
-        <v>5665.3329999999987</v>
+        <v>10515.762</v>
       </c>
       <c r="F22">
-        <v>7092.5800000000017</v>
+        <v>15704.074</v>
       </c>
       <c r="G22">
-        <v>7402.4480000000003</v>
+        <v>15363.809</v>
       </c>
       <c r="H22">
-        <v>6767.4889999999978</v>
+        <v>16043.561</v>
       </c>
       <c r="I22">
-        <v>96914262.779000014</v>
+        <v>171611025.7</v>
       </c>
       <c r="J22">
-        <v>98198917.545000017</v>
+        <v>166126931.487</v>
       </c>
       <c r="K22">
-        <v>95401337.704000026</v>
+        <v>177022875.975</v>
       </c>
       <c r="L22">
-        <v>942950702.60599995</v>
+        <v>2088335833.485</v>
       </c>
       <c r="M22">
-        <v>984466705.09899998</v>
+        <v>2042932356.495</v>
       </c>
       <c r="N22">
-        <v>899556269.52999973</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
+        <v>2133698588.262</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C23">
-        <v>-1578.39499999999</v>
+        <v>83655.99400000001</v>
       </c>
       <c r="D23">
-        <v>2305.51999999999</v>
+        <v>82178.63999999998</v>
       </c>
       <c r="E23">
-        <v>-5574.2569999999832</v>
+        <v>85026.87700000001</v>
       </c>
       <c r="F23">
-        <v>-3099.5270000000019</v>
+        <v>24587.65800000001</v>
       </c>
       <c r="G23">
-        <v>-1375.038</v>
+        <v>23971.63399999999</v>
       </c>
       <c r="H23">
-        <v>-4978.3709999999992</v>
+        <v>25141.373</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1480,83 +1473,91 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>-412772010.1439991</v>
+        <v>3270288122.848</v>
       </c>
       <c r="M23">
-        <v>-182483947.21399969</v>
+        <v>3190618669.623</v>
       </c>
       <c r="N23">
-        <v>-663861935.95099926</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
+        <v>3340744630.454999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C24">
-        <v>-249.00500000000099</v>
+        <v>3350.769</v>
       </c>
       <c r="D24">
-        <v>-20.004000000000811</v>
+        <v>3359.877999999999</v>
       </c>
       <c r="E24">
-        <v>-491.09699999999879</v>
+        <v>3329.713000000001</v>
       </c>
       <c r="F24">
-        <v>-966.14799999999923</v>
+        <v>6111.339999999998</v>
       </c>
       <c r="G24">
-        <v>-492.93599999999969</v>
+        <v>6138.369000000001</v>
       </c>
       <c r="H24">
-        <v>-1472.388999999999</v>
+        <v>6068.299999999999</v>
       </c>
       <c r="I24">
-        <v>-18755648.936000049</v>
+        <v>251959628.5270001</v>
       </c>
       <c r="J24">
-        <v>-1513211.1679999831</v>
+        <v>252858756.767</v>
       </c>
       <c r="K24">
-        <v>-36987842.145000041</v>
+        <v>250553308.8959999</v>
       </c>
       <c r="L24">
-        <v>-128370919.2460001</v>
+        <v>812954314.569</v>
       </c>
       <c r="M24">
-        <v>-65552398.430000067</v>
+        <v>816182895.9089999</v>
       </c>
       <c r="N24">
-        <v>-195520871.3510001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
+        <v>806881419.5970001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C25">
-        <v>41306.088999999993</v>
+        <v>51999.48799999999</v>
       </c>
       <c r="D25">
-        <v>39949.934000000001</v>
+        <v>49984.503</v>
       </c>
       <c r="E25">
-        <v>42656.641000000003</v>
+        <v>54005.59800000001</v>
       </c>
       <c r="F25">
-        <v>370423.18300000019</v>
+        <v>506595.443</v>
       </c>
       <c r="G25">
-        <v>367273.30400000012</v>
+        <v>497356.4710000001</v>
       </c>
       <c r="H25">
-        <v>373500.58200000011</v>
+        <v>515740.5249999999</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1568,237 +1569,256 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>49268072625.200012</v>
+        <v>67378465904.261</v>
       </c>
       <c r="M25">
-        <v>48845991701.009987</v>
+        <v>66153932771.45898</v>
       </c>
       <c r="N25">
-        <v>49679111585.875</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>15</v>
+        <v>68605508571.31499</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C26">
-        <v>40631.329000000012</v>
+        <v>73314.098</v>
       </c>
       <c r="D26">
-        <v>41191.27900000001</v>
+        <v>71395.31299999999</v>
       </c>
       <c r="E26">
-        <v>39969.97099999999</v>
+        <v>75156.54599999999</v>
       </c>
       <c r="F26">
-        <v>168637.84299999999</v>
+        <v>220032.362</v>
       </c>
       <c r="G26">
-        <v>167101.50399999999</v>
+        <v>215104.991</v>
       </c>
       <c r="H26">
-        <v>169880.37100000001</v>
+        <v>224788.646</v>
       </c>
       <c r="I26">
-        <v>570252554.255</v>
+        <v>938206488.5949999</v>
       </c>
       <c r="J26">
-        <v>574343220.87300003</v>
+        <v>917102596.1279999</v>
       </c>
       <c r="K26">
-        <v>565189628.20799994</v>
+        <v>958844886.622</v>
       </c>
       <c r="L26">
-        <v>22427095456.580009</v>
+        <v>29264056705.31301</v>
       </c>
       <c r="M26">
-        <v>22229968892.318001</v>
+        <v>28612351301.404</v>
       </c>
       <c r="N26">
-        <v>22591907563.271011</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
+        <v>29900229479.58</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C27">
-        <v>30023.829999999991</v>
+        <v>58679.575</v>
       </c>
       <c r="D27">
-        <v>30984.24400000001</v>
+        <v>57423.94</v>
       </c>
       <c r="E27">
-        <v>28996.886999999999</v>
+        <v>59880.04399999999</v>
       </c>
       <c r="F27">
-        <v>149993.495</v>
+        <v>203156.933</v>
       </c>
       <c r="G27">
-        <v>150604.34700000001</v>
+        <v>200230.763</v>
       </c>
       <c r="H27">
-        <v>149212.7000000001</v>
+        <v>205962.7339999999</v>
       </c>
       <c r="I27">
-        <v>395687388.93199998</v>
+        <v>723090657.762</v>
       </c>
       <c r="J27">
-        <v>412674929.32800013</v>
+        <v>712786338.724</v>
       </c>
       <c r="K27">
-        <v>377410125.56900012</v>
+        <v>732681491.1639999</v>
       </c>
       <c r="L27">
-        <v>19949807496.519001</v>
+        <v>27018222328.56001</v>
       </c>
       <c r="M27">
-        <v>20030299351.564991</v>
+        <v>26632764005.51</v>
       </c>
       <c r="N27">
-        <v>19847513956.016998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" t="s">
-        <v>17</v>
+        <v>27396563361.958</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C28">
-        <v>-11462.47900000001</v>
+        <v>61124.59599999999</v>
       </c>
       <c r="D28">
-        <v>-8608.4670000000042</v>
+        <v>59948.69199999998</v>
       </c>
       <c r="E28">
-        <v>-14385.571</v>
+        <v>62246.12299999999</v>
       </c>
       <c r="F28">
-        <v>60309.584999999897</v>
+        <v>173177.0269999998</v>
       </c>
       <c r="G28">
-        <v>63401.689999999937</v>
+        <v>170645.88</v>
       </c>
       <c r="H28">
-        <v>57081.242000000137</v>
+        <v>175657.3680000001</v>
       </c>
       <c r="I28">
-        <v>-85791992.407999992</v>
+        <v>644428630.2820001</v>
       </c>
       <c r="J28">
-        <v>-51550765.082999937</v>
+        <v>636554486.938</v>
       </c>
       <c r="K28">
-        <v>-120783006.65800001</v>
+        <v>651797909.7519999</v>
       </c>
       <c r="L28">
-        <v>8023657825.473999</v>
+        <v>23036278689.75401</v>
       </c>
       <c r="M28">
-        <v>8425487743.4929962</v>
+        <v>22697320249.645</v>
       </c>
       <c r="N28">
-        <v>7593888337.0370102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
+        <v>23363477748.606</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C29">
-        <v>59192.679999999993</v>
+        <v>193118.2689999999</v>
       </c>
       <c r="D29">
-        <v>63567.055999999982</v>
+        <v>188767.9449999999</v>
       </c>
       <c r="E29">
-        <v>54581.286999999887</v>
+        <v>197282.7129999999</v>
       </c>
       <c r="F29">
-        <v>378940.92300000013</v>
+        <v>596366.322</v>
       </c>
       <c r="G29">
-        <v>381107.54099999991</v>
+        <v>585981.6339999997</v>
       </c>
       <c r="H29">
-        <v>376174.31300000002</v>
+        <v>606408.748</v>
       </c>
       <c r="I29">
-        <v>880147950.77899981</v>
+        <v>2305725776.639</v>
       </c>
       <c r="J29">
-        <v>935467385.11800003</v>
+        <v>2266443421.789999</v>
       </c>
       <c r="K29">
-        <v>821816747.11900043</v>
+        <v>2343324287.537999</v>
       </c>
       <c r="L29">
-        <v>50400560778.572998</v>
+        <v>79318557723.62701</v>
       </c>
       <c r="M29">
-        <v>50685755987.375992</v>
+        <v>77942435556.5591</v>
       </c>
       <c r="N29">
-        <v>50033309856.325104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" t="s">
-        <v>23</v>
+        <v>80660270590.14401</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Morbidity</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C30">
-        <v>17886.591000000011</v>
+        <v>141118.781</v>
       </c>
       <c r="D30">
-        <v>23617.121999999999</v>
+        <v>138783.442</v>
       </c>
       <c r="E30">
-        <v>11924.645999999981</v>
+        <v>143277.115</v>
       </c>
       <c r="F30">
-        <v>8517.7399999999907</v>
+        <v>89770.87900000002</v>
       </c>
       <c r="G30">
-        <v>13834.237000000019</v>
+        <v>88625.163</v>
       </c>
       <c r="H30">
-        <v>2673.7309999998829</v>
+        <v>90668.22300000011</v>
       </c>
       <c r="I30">
-        <v>880147950.77899981</v>
+        <v>2305725776.639</v>
       </c>
       <c r="J30">
-        <v>935467385.11800003</v>
+        <v>2266443421.789999</v>
       </c>
       <c r="K30">
-        <v>821816747.11900043</v>
+        <v>2343324287.537999</v>
       </c>
       <c r="L30">
-        <v>1132488153.372997</v>
+        <v>11940091819.366</v>
       </c>
       <c r="M30">
-        <v>1839764286.3659971</v>
+        <v>11788502785.1</v>
       </c>
       <c r="N30">
-        <v>354198270.45000082</v>
+        <v>12054762018.829</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N30" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
@@ -1,21 +1,123 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E14EA05-3C06-BC46-9107-E0CF0AF7AF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="27240" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$30</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>area_type</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>periurban</t>
+  </si>
+  <si>
+    <t>rural</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +165,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +217,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +251,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +286,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,110 +462,89 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>area_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>19509.293</v>
+        <v>19509.293000000001</v>
       </c>
       <c r="D2">
-        <v>18673.639</v>
+        <v>18673.638999999999</v>
       </c>
       <c r="E2">
-        <v>20342.699</v>
+        <v>20342.699000000001</v>
       </c>
       <c r="F2">
-        <v>185393.338</v>
+        <v>185393.33799999999</v>
       </c>
       <c r="G2">
-        <v>181100.034</v>
+        <v>181100.03400000001</v>
       </c>
       <c r="H2">
-        <v>189629.224</v>
+        <v>189629.22399999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,40 +556,36 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>24656879688.883</v>
+        <v>24656879688.882999</v>
       </c>
       <c r="M2">
-        <v>24089737440.448</v>
+        <v>24089737440.448002</v>
       </c>
       <c r="N2">
-        <v>25225865688.877</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>25225865688.876999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>18845.975</v>
+        <v>18845.974999999999</v>
       </c>
       <c r="D3">
-        <v>18147.743</v>
+        <v>18147.742999999999</v>
       </c>
       <c r="E3">
         <v>19536.427</v>
       </c>
       <c r="F3">
-        <v>177400.037</v>
+        <v>177400.03700000001</v>
       </c>
       <c r="G3">
-        <v>174718.727</v>
+        <v>174718.72700000001</v>
       </c>
       <c r="H3">
         <v>180027.821</v>
@@ -513,31 +600,27 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>23591860969.302</v>
+        <v>23591860969.301998</v>
       </c>
       <c r="M3">
         <v>23240531183.743</v>
       </c>
       <c r="N3">
-        <v>23946733077.677</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>23946733077.676998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
         <v>13644.22</v>
       </c>
       <c r="D4">
-        <v>13163.121</v>
+        <v>13163.120999999999</v>
       </c>
       <c r="E4">
         <v>14126.472</v>
@@ -549,7 +632,7 @@
         <v>141537.71</v>
       </c>
       <c r="H4">
-        <v>146083.48</v>
+        <v>146083.48000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -564,97 +647,89 @@
         <v>19129725246.076</v>
       </c>
       <c r="M4">
-        <v>18823664147.268</v>
+        <v>18823664147.268002</v>
       </c>
       <c r="N4">
-        <v>19432909804.761</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>19432909804.761002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
       <c r="C5">
         <v>12225</v>
       </c>
       <c r="D5">
-        <v>11899.494</v>
+        <v>11899.494000000001</v>
       </c>
       <c r="E5">
         <v>12547.213</v>
       </c>
       <c r="F5">
-        <v>9997.686000000002</v>
+        <v>9997.6860000000015</v>
       </c>
       <c r="G5">
-        <v>9766.778999999999</v>
+        <v>9766.7789999999986</v>
       </c>
       <c r="H5">
         <v>10226.117</v>
       </c>
       <c r="I5">
-        <v>680972788.5039999</v>
+        <v>680972788.50399995</v>
       </c>
       <c r="J5">
-        <v>662904568.6479999</v>
+        <v>662904568.64799988</v>
       </c>
       <c r="K5">
-        <v>699128508.6719999</v>
+        <v>699128508.67199993</v>
       </c>
       <c r="L5">
-        <v>1329844702.133</v>
+        <v>1329844702.1329999</v>
       </c>
       <c r="M5">
-        <v>1299295319.196</v>
+        <v>1299295319.1960001</v>
       </c>
       <c r="N5">
         <v>1359679294.553</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>9591.328000000001</v>
+        <v>9591.3280000000013</v>
       </c>
       <c r="D6">
-        <v>9425.666999999999</v>
+        <v>9425.6669999999995</v>
       </c>
       <c r="E6">
-        <v>9757.661999999998</v>
+        <v>9757.6619999999984</v>
       </c>
       <c r="F6">
-        <v>7880.279</v>
+        <v>7880.2790000000005</v>
       </c>
       <c r="G6">
         <v>7781.686999999999</v>
       </c>
       <c r="H6">
-        <v>7976.136999999999</v>
+        <v>7976.1369999999988</v>
       </c>
       <c r="I6">
         <v>534258104.704</v>
       </c>
       <c r="J6">
-        <v>524762567.073</v>
+        <v>524762567.07300001</v>
       </c>
       <c r="K6">
-        <v>543478008.558</v>
+        <v>543478008.55799997</v>
       </c>
       <c r="L6">
         <v>1048270659.398</v>
@@ -666,163 +741,147 @@
         <v>1060515870.668</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
       </c>
       <c r="C7">
         <v>8302.130000000001</v>
       </c>
       <c r="D7">
-        <v>8149.454000000002</v>
+        <v>8149.4540000000025</v>
       </c>
       <c r="E7">
-        <v>8454.790999999997</v>
+        <v>8454.7909999999974</v>
       </c>
       <c r="F7">
-        <v>7338.808000000001</v>
+        <v>7338.8080000000009</v>
       </c>
       <c r="G7">
-        <v>7230.684000000001</v>
+        <v>7230.6840000000011</v>
       </c>
       <c r="H7">
-        <v>7445.133999999998</v>
+        <v>7445.1339999999982</v>
       </c>
       <c r="I7">
-        <v>462535922.313</v>
+        <v>462535922.31300002</v>
       </c>
       <c r="J7">
-        <v>453841101.9229999</v>
+        <v>453841101.92299992</v>
       </c>
       <c r="K7">
-        <v>471174495.0739999</v>
+        <v>471174495.07399988</v>
       </c>
       <c r="L7">
-        <v>975824629.3649998</v>
+        <v>975824629.36499977</v>
       </c>
       <c r="M7">
-        <v>962000053.302</v>
+        <v>962000053.30200005</v>
       </c>
       <c r="N7">
-        <v>989878200.4769998</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>989878200.47699976</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>5795.068</v>
+        <v>5795.0680000000002</v>
       </c>
       <c r="D8">
-        <v>5798.173</v>
+        <v>5798.1729999999998</v>
       </c>
       <c r="E8">
-        <v>5777.031000000001</v>
+        <v>5777.0310000000009</v>
       </c>
       <c r="F8">
-        <v>7315.199000000001</v>
+        <v>7315.1990000000014</v>
       </c>
       <c r="G8">
-        <v>7346.737999999999</v>
+        <v>7346.7379999999994</v>
       </c>
       <c r="H8">
         <v>7225.523000000001</v>
       </c>
       <c r="I8">
-        <v>85813551.79699999</v>
+        <v>85813551.796999991</v>
       </c>
       <c r="J8">
-        <v>85825047.37899998</v>
+        <v>85825047.378999978</v>
       </c>
       <c r="K8">
-        <v>85454810.846</v>
+        <v>85454810.846000001</v>
       </c>
       <c r="L8">
-        <v>973034696.424</v>
+        <v>973034696.42400002</v>
       </c>
       <c r="M8">
-        <v>977361583.5149999</v>
+        <v>977361583.51499987</v>
       </c>
       <c r="N8">
-        <v>961224868.7600002</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>961224868.76000023</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>4090.767</v>
+        <v>4090.7669999999998</v>
       </c>
       <c r="D9">
-        <v>4125.324000000001</v>
+        <v>4125.3240000000014</v>
       </c>
       <c r="E9">
-        <v>4042.592</v>
+        <v>4042.5920000000001</v>
       </c>
       <c r="F9">
-        <v>5232.619000000001</v>
+        <v>5232.6190000000006</v>
       </c>
       <c r="G9">
-        <v>5287.691999999999</v>
+        <v>5287.6919999999991</v>
       </c>
       <c r="H9">
-        <v>5130.632</v>
+        <v>5130.6319999999996</v>
       </c>
       <c r="I9">
-        <v>60606967.63300002</v>
+        <v>60606967.633000024</v>
       </c>
       <c r="J9">
-        <v>61105518.92799999</v>
+        <v>61105518.927999988</v>
       </c>
       <c r="K9">
         <v>59888950.206</v>
       </c>
       <c r="L9">
-        <v>696415583.0639999</v>
+        <v>696415583.06399989</v>
       </c>
       <c r="M9">
-        <v>702724229.803</v>
+        <v>702724229.80299997</v>
       </c>
       <c r="N9">
-        <v>683469851.3280001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>683469851.32800007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10">
-        <v>3917.314999999999</v>
+        <v>3917.3149999999991</v>
       </c>
       <c r="D10">
         <v>3982.407999999999</v>
@@ -831,43 +890,39 @@
         <v>3825.474000000002</v>
       </c>
       <c r="F10">
-        <v>5603.216</v>
+        <v>5603.2160000000003</v>
       </c>
       <c r="G10">
-        <v>5737.771000000001</v>
+        <v>5737.7710000000006</v>
       </c>
       <c r="H10">
-        <v>5411.445999999996</v>
+        <v>5411.4459999999963</v>
       </c>
       <c r="I10">
-        <v>57967787.46099997</v>
+        <v>57967787.460999973</v>
       </c>
       <c r="J10">
-        <v>59018929.58500001</v>
+        <v>59018929.585000008</v>
       </c>
       <c r="K10">
-        <v>56623329.31100002</v>
+        <v>56623329.311000019</v>
       </c>
       <c r="L10">
-        <v>745123278.0799999</v>
+        <v>745123278.07999992</v>
       </c>
       <c r="M10">
-        <v>763131959.8800001</v>
+        <v>763131959.88000011</v>
       </c>
       <c r="N10">
-        <v>718669294.7290001</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>718669294.72900009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
         <v>1342.347</v>
@@ -876,10 +931,10 @@
         <v>1335.412</v>
       </c>
       <c r="E11">
-        <v>1344.993</v>
+        <v>1344.9929999999999</v>
       </c>
       <c r="F11">
-        <v>2354.626</v>
+        <v>2354.6260000000002</v>
       </c>
       <c r="G11">
         <v>2342.195999999999</v>
@@ -894,40 +949,36 @@
         <v>100471617.177</v>
       </c>
       <c r="K11">
-        <v>101189032.547</v>
+        <v>101189032.54700001</v>
       </c>
       <c r="L11">
-        <v>313182030.589</v>
+        <v>313182030.58899999</v>
       </c>
       <c r="M11">
-        <v>311509148.828</v>
+        <v>311509148.82800001</v>
       </c>
       <c r="N11">
-        <v>314104775.193</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>314104775.19300002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>968.4570000000001</v>
+        <v>968.45700000000011</v>
       </c>
       <c r="D12">
-        <v>972.5599999999999</v>
+        <v>972.56</v>
       </c>
       <c r="E12">
-        <v>959.442</v>
+        <v>959.44200000000001</v>
       </c>
       <c r="F12">
-        <v>1719.321</v>
+        <v>1719.3209999999999</v>
       </c>
       <c r="G12">
         <v>1729.978000000001</v>
@@ -936,37 +987,33 @@
         <v>1703.296</v>
       </c>
       <c r="I12">
-        <v>72803132.08399999</v>
+        <v>72803132.083999991</v>
       </c>
       <c r="J12">
-        <v>73137005.20199999</v>
+        <v>73137005.201999992</v>
       </c>
       <c r="K12">
-        <v>72269620.84899999</v>
+        <v>72269620.848999992</v>
       </c>
       <c r="L12">
-        <v>228738049.385</v>
+        <v>228738049.38499999</v>
       </c>
       <c r="M12">
-        <v>229848161.783</v>
+        <v>229848161.78299999</v>
       </c>
       <c r="N12">
         <v>226438866.685</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>1039.965</v>
+        <v>1039.9649999999999</v>
       </c>
       <c r="D13">
         <v>1051.905999999999</v>
@@ -978,187 +1025,171 @@
         <v>2037.393</v>
       </c>
       <c r="G13">
-        <v>2066.195</v>
+        <v>2066.1950000000002</v>
       </c>
       <c r="H13">
-        <v>2001.955000000001</v>
+        <v>2001.9550000000011</v>
       </c>
       <c r="I13">
-        <v>78217742.23600003</v>
+        <v>78217742.236000031</v>
       </c>
       <c r="J13">
-        <v>79250134.38800001</v>
+        <v>79250134.388000011</v>
       </c>
       <c r="K13">
         <v>77094655.5</v>
       </c>
       <c r="L13">
-        <v>271034234.5949999</v>
+        <v>271034234.59499991</v>
       </c>
       <c r="M13">
         <v>274825585.2980001</v>
       </c>
       <c r="N13">
-        <v>266337777.7189999</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>266337777.71899989</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>4184.805</v>
+        <v>4184.8050000000003</v>
       </c>
       <c r="D14">
-        <v>4031.041</v>
+        <v>4031.0410000000002</v>
       </c>
       <c r="E14">
-        <v>4339.503</v>
+        <v>4339.5029999999997</v>
       </c>
       <c r="F14">
-        <v>6568.551</v>
+        <v>6568.5510000000004</v>
       </c>
       <c r="G14">
-        <v>6387.679999999999</v>
+        <v>6387.6799999999994</v>
       </c>
       <c r="H14">
-        <v>6746.357999999999</v>
+        <v>6746.3579999999993</v>
       </c>
       <c r="I14">
-        <v>70481394.08700001</v>
+        <v>70481394.087000012</v>
       </c>
       <c r="J14">
         <v>67901362.92400001</v>
       </c>
       <c r="K14">
-        <v>73072534.55700001</v>
+        <v>73072534.557000011</v>
       </c>
       <c r="L14">
-        <v>873354560.8449999</v>
+        <v>873354560.84499991</v>
       </c>
       <c r="M14">
-        <v>849336922.263</v>
+        <v>849336922.26300001</v>
       </c>
       <c r="N14">
-        <v>897261840.9779999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>897261840.97799993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
         <v>3292.027</v>
       </c>
       <c r="D15">
-        <v>3194.351</v>
+        <v>3194.3510000000001</v>
       </c>
       <c r="E15">
-        <v>3387.144</v>
+        <v>3387.1439999999998</v>
       </c>
       <c r="F15">
         <v>4836.26</v>
       </c>
       <c r="G15">
-        <v>4756.254</v>
+        <v>4756.2539999999999</v>
       </c>
       <c r="H15">
-        <v>4914.467000000001</v>
+        <v>4914.4670000000006</v>
       </c>
       <c r="I15">
-        <v>55422453.341</v>
+        <v>55422453.340999998</v>
       </c>
       <c r="J15">
-        <v>53781247.521</v>
+        <v>53781247.520999998</v>
       </c>
       <c r="K15">
-        <v>57044911.551</v>
+        <v>57044911.550999999</v>
       </c>
       <c r="L15">
-        <v>643168586.6019999</v>
+        <v>643168586.60199988</v>
       </c>
       <c r="M15">
         <v>632323333.9690001</v>
       </c>
       <c r="N15">
-        <v>653680524.081</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>653680524.08099997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
         <v>2713.578</v>
       </c>
       <c r="D16">
-        <v>2639.012</v>
+        <v>2639.0120000000002</v>
       </c>
       <c r="E16">
-        <v>2789.115000000001</v>
+        <v>2789.1150000000011</v>
       </c>
       <c r="F16">
-        <v>4299.263000000001</v>
+        <v>4299.2630000000008</v>
       </c>
       <c r="G16">
         <v>4219.875</v>
       </c>
       <c r="H16">
-        <v>4382.736000000001</v>
+        <v>4382.7360000000008</v>
       </c>
       <c r="I16">
-        <v>45707178.27199998</v>
+        <v>45707178.271999978</v>
       </c>
       <c r="J16">
-        <v>44444321.042</v>
+        <v>44444321.042000003</v>
       </c>
       <c r="K16">
-        <v>46905429.867</v>
+        <v>46905429.866999999</v>
       </c>
       <c r="L16">
-        <v>571812686.0380001</v>
+        <v>571812686.03800011</v>
       </c>
       <c r="M16">
-        <v>561272100.263</v>
+        <v>561272100.26300001</v>
       </c>
       <c r="N16">
-        <v>582756223.2029998</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>582756223.20299983</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>30257.585</v>
+        <v>30257.584999999999</v>
       </c>
       <c r="D17">
         <v>29657.554</v>
@@ -1167,13 +1198,13 @@
         <v>30805.107</v>
       </c>
       <c r="F17">
-        <v>8402.962</v>
+        <v>8402.9619999999995</v>
       </c>
       <c r="G17">
-        <v>8161.563999999999</v>
+        <v>8161.5639999999994</v>
       </c>
       <c r="H17">
-        <v>8598.375000000002</v>
+        <v>8598.3750000000018</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,43 +1216,39 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1117761026.439</v>
+        <v>1117761026.4389999</v>
       </c>
       <c r="M17">
         <v>1085110887.154</v>
       </c>
       <c r="N17">
-        <v>1142093011.219</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>1142093011.2190001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>21891.021</v>
+        <v>21891.021000000001</v>
       </c>
       <c r="D18">
-        <v>21558.295</v>
+        <v>21558.294999999998</v>
       </c>
       <c r="E18">
-        <v>22196.777</v>
+        <v>22196.776999999998</v>
       </c>
       <c r="F18">
-        <v>6088.416999999999</v>
+        <v>6088.4169999999986</v>
       </c>
       <c r="G18">
-        <v>5956.425</v>
+        <v>5956.4250000000002</v>
       </c>
       <c r="H18">
-        <v>6210.381000000001</v>
+        <v>6210.3810000000012</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,40 +1260,36 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>809768480.8090001</v>
+        <v>809768480.80900013</v>
       </c>
       <c r="M18">
-        <v>793081378.835</v>
+        <v>793081378.83500004</v>
       </c>
       <c r="N18">
-        <v>825725171.5190001</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>825725171.51900005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
       </c>
       <c r="C19">
-        <v>31507.38799999999</v>
+        <v>31507.387999999992</v>
       </c>
       <c r="D19">
-        <v>30962.791</v>
+        <v>30962.791000000001</v>
       </c>
       <c r="E19">
-        <v>32024.993</v>
+        <v>32024.992999999999</v>
       </c>
       <c r="F19">
         <v>10096.279</v>
       </c>
       <c r="G19">
-        <v>9853.644999999997</v>
+        <v>9853.6449999999968</v>
       </c>
       <c r="H19">
         <v>10332.617</v>
@@ -1281,31 +1304,27 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>1342758615.6</v>
+        <v>1342758615.5999999</v>
       </c>
       <c r="M19">
-        <v>1312426403.634</v>
+        <v>1312426403.6340001</v>
       </c>
       <c r="N19">
         <v>1372926447.717</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
       </c>
       <c r="C20">
         <v>13803.15</v>
       </c>
       <c r="D20">
-        <v>13905.905</v>
+        <v>13905.905000000001</v>
       </c>
       <c r="E20">
         <v>13645.09700000002</v>
@@ -1314,22 +1333,22 @@
         <v>18151.034</v>
       </c>
       <c r="G20">
-        <v>18372.201</v>
+        <v>18372.201000000001</v>
       </c>
       <c r="H20">
-        <v>17767.601</v>
+        <v>17767.600999999999</v>
       </c>
       <c r="I20">
         <v>204388306.891</v>
       </c>
       <c r="J20">
-        <v>205949495.892</v>
+        <v>205949495.89199999</v>
       </c>
       <c r="K20">
-        <v>201967090.3630001</v>
+        <v>201967090.36300009</v>
       </c>
       <c r="L20">
-        <v>2414573557.567999</v>
+        <v>2414573557.5679989</v>
       </c>
       <c r="M20">
         <v>2443217773.198</v>
@@ -1338,46 +1357,42 @@
         <v>2363364014.816999</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
       </c>
       <c r="C21">
         <v>30118.45800000001</v>
       </c>
       <c r="D21">
-        <v>29474.61500000001</v>
+        <v>29474.615000000009</v>
       </c>
       <c r="E21">
-        <v>30759.666</v>
+        <v>30759.666000000001</v>
       </c>
       <c r="F21">
-        <v>25216.77300000001</v>
+        <v>25216.773000000008</v>
       </c>
       <c r="G21">
         <v>24779.15</v>
       </c>
       <c r="H21">
-        <v>25647.388</v>
+        <v>25647.387999999999</v>
       </c>
       <c r="I21">
-        <v>1677766815.521</v>
+        <v>1677766815.5209999</v>
       </c>
       <c r="J21">
-        <v>1641508237.644</v>
+        <v>1641508237.6440001</v>
       </c>
       <c r="K21">
-        <v>1713781012.304</v>
+        <v>1713781012.3039999</v>
       </c>
       <c r="L21">
-        <v>3353939990.896</v>
+        <v>3353939990.8959999</v>
       </c>
       <c r="M21">
         <v>3295551089.875</v>
@@ -1386,79 +1401,71 @@
         <v>3410073365.698</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
       </c>
       <c r="C22">
         <v>10190.41</v>
       </c>
       <c r="D22">
-        <v>9864.404000000002</v>
+        <v>9864.4040000000023</v>
       </c>
       <c r="E22">
-        <v>10515.762</v>
+        <v>10515.762000000001</v>
       </c>
       <c r="F22">
-        <v>15704.074</v>
+        <v>15704.074000000001</v>
       </c>
       <c r="G22">
-        <v>15363.809</v>
+        <v>15363.808999999999</v>
       </c>
       <c r="H22">
         <v>16043.561</v>
       </c>
       <c r="I22">
-        <v>171611025.7</v>
+        <v>171611025.69999999</v>
       </c>
       <c r="J22">
-        <v>166126931.487</v>
+        <v>166126931.48699999</v>
       </c>
       <c r="K22">
-        <v>177022875.975</v>
+        <v>177022875.97499999</v>
       </c>
       <c r="L22">
-        <v>2088335833.485</v>
+        <v>2088335833.4849999</v>
       </c>
       <c r="M22">
-        <v>2042932356.495</v>
+        <v>2042932356.4949999</v>
       </c>
       <c r="N22">
-        <v>2133698588.262</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>2133698588.2620001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
       </c>
       <c r="C23">
-        <v>83655.99400000001</v>
+        <v>83655.994000000006</v>
       </c>
       <c r="D23">
-        <v>82178.63999999998</v>
+        <v>82178.639999999985</v>
       </c>
       <c r="E23">
-        <v>85026.87700000001</v>
+        <v>85026.877000000008</v>
       </c>
       <c r="F23">
         <v>24587.65800000001</v>
       </c>
       <c r="G23">
-        <v>23971.63399999999</v>
+        <v>23971.633999999991</v>
       </c>
       <c r="H23">
         <v>25141.373</v>
@@ -1476,88 +1483,80 @@
         <v>3270288122.848</v>
       </c>
       <c r="M23">
-        <v>3190618669.623</v>
+        <v>3190618669.6230001</v>
       </c>
       <c r="N23">
         <v>3340744630.454999</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>3350.769</v>
+        <v>3350.7689999999998</v>
       </c>
       <c r="D24">
-        <v>3359.877999999999</v>
+        <v>3359.8779999999988</v>
       </c>
       <c r="E24">
-        <v>3329.713000000001</v>
+        <v>3329.7130000000011</v>
       </c>
       <c r="F24">
-        <v>6111.339999999998</v>
+        <v>6111.3399999999983</v>
       </c>
       <c r="G24">
-        <v>6138.369000000001</v>
+        <v>6138.3690000000006</v>
       </c>
       <c r="H24">
-        <v>6068.299999999999</v>
+        <v>6068.2999999999993</v>
       </c>
       <c r="I24">
         <v>251959628.5270001</v>
       </c>
       <c r="J24">
-        <v>252858756.767</v>
+        <v>252858756.76699999</v>
       </c>
       <c r="K24">
-        <v>250553308.8959999</v>
+        <v>250553308.89599991</v>
       </c>
       <c r="L24">
-        <v>812954314.569</v>
+        <v>812954314.56900001</v>
       </c>
       <c r="M24">
-        <v>816182895.9089999</v>
+        <v>816182895.90899992</v>
       </c>
       <c r="N24">
-        <v>806881419.5970001</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>806881419.59700012</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
       </c>
       <c r="C25">
         <v>51999.48799999999</v>
       </c>
       <c r="D25">
-        <v>49984.503</v>
+        <v>49984.502999999997</v>
       </c>
       <c r="E25">
-        <v>54005.59800000001</v>
+        <v>54005.598000000013</v>
       </c>
       <c r="F25">
-        <v>506595.443</v>
+        <v>506595.44300000003</v>
       </c>
       <c r="G25">
-        <v>497356.4710000001</v>
+        <v>497356.47100000008</v>
       </c>
       <c r="H25">
-        <v>515740.5249999999</v>
+        <v>515740.52499999991</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1569,130 +1568,118 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>67378465904.261</v>
+        <v>67378465904.261002</v>
       </c>
       <c r="M25">
-        <v>66153932771.45898</v>
+        <v>66153932771.458977</v>
       </c>
       <c r="N25">
-        <v>68605508571.31499</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>68605508571.314987</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>73314.098</v>
+        <v>73314.097999999998</v>
       </c>
       <c r="D26">
-        <v>71395.31299999999</v>
+        <v>71395.312999999995</v>
       </c>
       <c r="E26">
-        <v>75156.54599999999</v>
+        <v>75156.545999999988</v>
       </c>
       <c r="F26">
-        <v>220032.362</v>
+        <v>220032.36199999999</v>
       </c>
       <c r="G26">
-        <v>215104.991</v>
+        <v>215104.99100000001</v>
       </c>
       <c r="H26">
-        <v>224788.646</v>
+        <v>224788.64600000001</v>
       </c>
       <c r="I26">
-        <v>938206488.5949999</v>
+        <v>938206488.59499991</v>
       </c>
       <c r="J26">
         <v>917102596.1279999</v>
       </c>
       <c r="K26">
-        <v>958844886.622</v>
+        <v>958844886.62199998</v>
       </c>
       <c r="L26">
-        <v>29264056705.31301</v>
+        <v>29264056705.313011</v>
       </c>
       <c r="M26">
-        <v>28612351301.404</v>
+        <v>28612351301.403999</v>
       </c>
       <c r="N26">
-        <v>29900229479.58</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>29900229479.580002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>58679.575</v>
+        <v>58679.574999999997</v>
       </c>
       <c r="D27">
         <v>57423.94</v>
       </c>
       <c r="E27">
-        <v>59880.04399999999</v>
+        <v>59880.043999999987</v>
       </c>
       <c r="F27">
-        <v>203156.933</v>
+        <v>203156.93299999999</v>
       </c>
       <c r="G27">
-        <v>200230.763</v>
+        <v>200230.76300000001</v>
       </c>
       <c r="H27">
-        <v>205962.7339999999</v>
+        <v>205962.73399999991</v>
       </c>
       <c r="I27">
-        <v>723090657.762</v>
+        <v>723090657.76199996</v>
       </c>
       <c r="J27">
-        <v>712786338.724</v>
+        <v>712786338.72399998</v>
       </c>
       <c r="K27">
-        <v>732681491.1639999</v>
+        <v>732681491.16399992</v>
       </c>
       <c r="L27">
-        <v>27018222328.56001</v>
+        <v>27018222328.560009</v>
       </c>
       <c r="M27">
-        <v>26632764005.51</v>
+        <v>26632764005.509998</v>
       </c>
       <c r="N27">
         <v>27396563361.958</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
       </c>
       <c r="C28">
         <v>61124.59599999999</v>
       </c>
       <c r="D28">
-        <v>59948.69199999998</v>
+        <v>59948.691999999981</v>
       </c>
       <c r="E28">
-        <v>62246.12299999999</v>
+        <v>62246.122999999992</v>
       </c>
       <c r="F28">
         <v>173177.0269999998</v>
@@ -1704,112 +1691,104 @@
         <v>175657.3680000001</v>
       </c>
       <c r="I28">
-        <v>644428630.2820001</v>
+        <v>644428630.28200006</v>
       </c>
       <c r="J28">
-        <v>636554486.938</v>
+        <v>636554486.93799996</v>
       </c>
       <c r="K28">
-        <v>651797909.7519999</v>
+        <v>651797909.75199986</v>
       </c>
       <c r="L28">
-        <v>23036278689.75401</v>
+        <v>23036278689.754009</v>
       </c>
       <c r="M28">
         <v>22697320249.645</v>
       </c>
       <c r="N28">
-        <v>23363477748.606</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>23363477748.605999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
       </c>
       <c r="C29">
-        <v>193118.2689999999</v>
+        <v>193118.26899999991</v>
       </c>
       <c r="D29">
-        <v>188767.9449999999</v>
+        <v>188767.94499999989</v>
       </c>
       <c r="E29">
         <v>197282.7129999999</v>
       </c>
       <c r="F29">
-        <v>596366.322</v>
+        <v>596366.32200000004</v>
       </c>
       <c r="G29">
-        <v>585981.6339999997</v>
+        <v>585981.63399999973</v>
       </c>
       <c r="H29">
-        <v>606408.748</v>
+        <v>606408.74800000002</v>
       </c>
       <c r="I29">
-        <v>2305725776.639</v>
+        <v>2305725776.6389999</v>
       </c>
       <c r="J29">
         <v>2266443421.789999</v>
       </c>
       <c r="K29">
-        <v>2343324287.537999</v>
+        <v>2343324287.5379992</v>
       </c>
       <c r="L29">
-        <v>79318557723.62701</v>
+        <v>79318557723.627014</v>
       </c>
       <c r="M29">
-        <v>77942435556.5591</v>
+        <v>77942435556.559097</v>
       </c>
       <c r="N29">
-        <v>80660270590.14401</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>80660270590.144012</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
       </c>
       <c r="C30">
-        <v>141118.781</v>
+        <v>141118.78099999999</v>
       </c>
       <c r="D30">
-        <v>138783.442</v>
+        <v>138783.44200000001</v>
       </c>
       <c r="E30">
-        <v>143277.115</v>
+        <v>143277.11499999999</v>
       </c>
       <c r="F30">
-        <v>89770.87900000002</v>
+        <v>89770.879000000015</v>
       </c>
       <c r="G30">
         <v>88625.163</v>
       </c>
       <c r="H30">
-        <v>90668.22300000011</v>
+        <v>90668.223000000115</v>
       </c>
       <c r="I30">
-        <v>2305725776.639</v>
+        <v>2305725776.6389999</v>
       </c>
       <c r="J30">
         <v>2266443421.789999</v>
       </c>
       <c r="K30">
-        <v>2343324287.537999</v>
+        <v>2343324287.5379992</v>
       </c>
       <c r="L30">
-        <v>11940091819.366</v>
+        <v>11940091819.365999</v>
       </c>
       <c r="M30">
         <v>11788502785.1</v>
@@ -1819,6 +1798,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N30" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E14EA05-3C06-BC46-9107-E0CF0AF7AF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CF4EA9-F4EC-144F-812E-5C2C163F312A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="27240" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CF4EA9-F4EC-144F-812E-5C2C163F312A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1F9391-03A5-3248-9370-EDC98640E414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="27240" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
